--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -38,6 +38,18 @@
     <t>desc</t>
   </si>
   <si>
+    <t>damage_value</t>
+  </si>
+  <si>
+    <t>shield_value</t>
+  </si>
+  <si>
+    <t>health_value</t>
+  </si>
+  <si>
+    <t>health_limit_value</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -45,6 +57,9 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
   <si>
     <t>##group</t>
@@ -1071,14 +1086,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
     <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
+    <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
+    <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
+    <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:3">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1088,61 +1106,97 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3">
+        <v>15</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3">
+        <v>17</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:3">

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +50,9 @@
     <t>health_limit_value</t>
   </si>
   <si>
+    <t>end_round_when_use</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>打出后结束回合?</t>
   </si>
   <si>
     <t>杀</t>
@@ -1086,17 +1095,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
     <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
     <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
     <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
     <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
+    <col min="7" max="7" width="17.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1118,84 +1128,105 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
+        <v>15</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8">
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:5">
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8">
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="2:6">
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="2:7">
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="97">
   <si>
     <t>##var</t>
   </si>
@@ -38,19 +38,22 @@
     <t>desc</t>
   </si>
   <si>
-    <t>damage_value</t>
-  </si>
-  <si>
-    <t>shield_value</t>
-  </si>
-  <si>
-    <t>health_value</t>
-  </si>
-  <si>
-    <t>health_limit_value</t>
-  </si>
-  <si>
-    <t>end_round_when_use</t>
+    <t>value</t>
+  </si>
+  <si>
+    <t>阎王面具</t>
+  </si>
+  <si>
+    <t>无常面具</t>
+  </si>
+  <si>
+    <t>阎罗面具</t>
+  </si>
+  <si>
+    <t>孟婆面具</t>
+  </si>
+  <si>
+    <t>二郎神面具</t>
   </si>
   <si>
     <t>##type</t>
@@ -59,13 +62,13 @@
     <t>CardEnum</t>
   </si>
   <si>
+    <t>CardTypeEnum</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>bool</t>
+    <t>(array#sep=;),int</t>
   </si>
   <si>
     <t>##group</t>
@@ -74,34 +77,247 @@
     <t>##</t>
   </si>
   <si>
+    <t>卡牌名</t>
+  </si>
+  <si>
     <t>描述</t>
   </si>
   <si>
-    <t>打出后结束回合?</t>
-  </si>
-  <si>
-    <t>杀</t>
-  </si>
-  <si>
-    <t>造成一点伤害</t>
-  </si>
-  <si>
-    <t>盾</t>
-  </si>
-  <si>
-    <t>获得一点护盾</t>
-  </si>
-  <si>
-    <t>桃</t>
-  </si>
-  <si>
-    <t>恢复一点生命值</t>
-  </si>
-  <si>
-    <t>好桃</t>
-  </si>
-  <si>
-    <t>增加一点生命上限</t>
+    <t>轻击</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害。</t>
+  </si>
+  <si>
+    <t>阎王轻击</t>
+  </si>
+  <si>
+    <t>无常轻击</t>
+  </si>
+  <si>
+    <t>孟婆熬药攻击</t>
+  </si>
+  <si>
+    <t>二郎神攻击</t>
+  </si>
+  <si>
+    <t>震慑</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，有{1}%的几率斩杀对手。打出后有{2}%的几率结束回合。</t>
+  </si>
+  <si>
+    <t>2;10;10</t>
+  </si>
+  <si>
+    <t>阎王震慑</t>
+  </si>
+  <si>
+    <t>无常震慑</t>
+  </si>
+  <si>
+    <t>阎罗震慑</t>
+  </si>
+  <si>
+    <t>万我</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>1;0;1;100</t>
+  </si>
+  <si>
+    <t>阎王万我</t>
+  </si>
+  <si>
+    <t>无常万我</t>
+  </si>
+  <si>
+    <t>吸魂</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。</t>
+  </si>
+  <si>
+    <t>1;5</t>
+  </si>
+  <si>
+    <t>阎王吸魂</t>
+  </si>
+  <si>
+    <t>无常吸魂</t>
+  </si>
+  <si>
+    <t>阎罗吸魂</t>
+  </si>
+  <si>
+    <t>炼魂</t>
+  </si>
+  <si>
+    <t>功能</t>
+  </si>
+  <si>
+    <t>获得{0}点护甲。</t>
+  </si>
+  <si>
+    <t>阎王炼魂</t>
+  </si>
+  <si>
+    <t>孟婆熬药功能</t>
+  </si>
+  <si>
+    <t>慷慨</t>
+  </si>
+  <si>
+    <t>受到{0}点伤害，然后摸{1}张牌。</t>
+  </si>
+  <si>
+    <t>2;2</t>
+  </si>
+  <si>
+    <t>阎王慷慨</t>
+  </si>
+  <si>
+    <t>静心</t>
+  </si>
+  <si>
+    <t>获得{0}点护甲。打出后有{1}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>3;100</t>
+  </si>
+  <si>
+    <t>阎王静心</t>
+  </si>
+  <si>
+    <t>养神</t>
+  </si>
+  <si>
+    <t>恢复{0}点生命。如果本回合中你打出过此牌的次数不小于{1}，有{2}%几率结束结束回合。</t>
+  </si>
+  <si>
+    <t>2;2;100</t>
+  </si>
+  <si>
+    <t>自力更生</t>
+  </si>
+  <si>
+    <t>视为打出本回合中你上一次打出的牌。打出后有{0}%几率结束结束回合。</t>
+  </si>
+  <si>
+    <t>无常自力</t>
+  </si>
+  <si>
+    <t>碎魂</t>
+  </si>
+  <si>
+    <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>2;0;100</t>
+  </si>
+  <si>
+    <t>阎王碎魂</t>
+  </si>
+  <si>
+    <t>壮魂</t>
+  </si>
+  <si>
+    <t>请神</t>
+  </si>
+  <si>
+    <t>直到你的下个回合结束时，当你造成伤害时，你获得{0}点护甲。</t>
+  </si>
+  <si>
+    <t>孟婆熬药请神</t>
+  </si>
+  <si>
+    <t>傩戏开场</t>
+  </si>
+  <si>
+    <t>傩戏开场！</t>
+  </si>
+  <si>
+    <t>直到你的回合结束时，随机佩戴一个面具（从十殿阎罗、孟婆、二郎真君中随机选择）。</t>
+  </si>
+  <si>
+    <t>面具傩戏</t>
+  </si>
+  <si>
+    <t>阎罗傩戏</t>
+  </si>
+  <si>
+    <t>二郎神请神</t>
+  </si>
+  <si>
+    <t>2;20;10</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
+  </si>
+  <si>
+    <t>1;0;1;100;5;1</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，获得{1}点护甲。</t>
+  </si>
+  <si>
+    <t>1;2</t>
+  </si>
+  <si>
+    <t>获得{0}点护甲，然后摸{1}张牌。</t>
+  </si>
+  <si>
+    <t>1;1</t>
+  </si>
+  <si>
+    <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。敌人的死期减少{3}。</t>
+  </si>
+  <si>
+    <t>2;0;100;1</t>
+  </si>
+  <si>
+    <t>此牌无效。</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，有{1}%的几率斩杀对手。打出后有{2}%的几率结束回合。有{3}%的概率额外打出一次此牌。</t>
+  </si>
+  <si>
+    <t>2;10;10;50</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>1;0;50;3;1;100</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。有{2}%的概率额外打出一次此牌。</t>
+  </si>
+  <si>
+    <t>1;5;50</t>
+  </si>
+  <si>
+    <t>2;30;30</t>
+  </si>
+  <si>
+    <t>3;3</t>
+  </si>
+  <si>
+    <t>随机切换一个律令（可能重复）。</t>
+  </si>
+  <si>
+    <t>孟婆汤中的攻击牌+1。</t>
+  </si>
+  <si>
+    <t>孟婆汤中的功能牌+1。</t>
+  </si>
+  <si>
+    <t>孟婆汤中的请神牌+1。</t>
   </si>
 </sst>
 </file>
@@ -114,9 +330,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -627,137 +850,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -773,7 +996,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1095,18 +1327,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
-    <col min="3" max="3" width="20.9732142857143" customWidth="1"/>
-    <col min="4" max="4" width="15.1696428571429" customWidth="1"/>
-    <col min="5" max="5" width="11.6071428571429" customWidth="1"/>
-    <col min="6" max="6" width="10.4196428571429" customWidth="1"/>
-    <col min="7" max="7" width="17.25" customWidth="1"/>
+    <col min="2" max="4" width="32.8916666666667" customWidth="1"/>
+    <col min="5" max="5" width="64.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1114,170 +1343,747 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:8">
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:1">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="3" customFormat="1" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="2:8">
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D5">
+      <c r="E5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="4">
         <v>1</v>
       </c>
-      <c r="H5" t="b">
+      <c r="G9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="4">
+        <v>100</v>
+      </c>
+      <c r="H13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="4" t="s">
+      <c r="J15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="4" t="s">
+      <c r="F26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-    </row>
-    <row r="10" spans="2:3">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" spans="2:3">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" spans="2:3">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" s="5"/>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" s="5"/>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" s="5"/>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="5"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="5"/>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="5"/>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="5"/>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="5"/>
+      <c r="C37" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardTable!$B$1:$B$38</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,12 +30,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
   </si>
   <si>
     <t>desc</t>
@@ -980,7 +986,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -997,12 +1003,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1343,403 +1343,403 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="E5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="B9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="7" t="s">
         <v>43</v>
       </c>
+      <c r="C9" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="D9" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="B10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
         <v>47</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="B11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>43</v>
+        <v>52</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="B12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="B13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>43</v>
+        <v>59</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="4">
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="B14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>43</v>
+        <v>62</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="B15" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="7" t="s">
         <v>66</v>
       </c>
+      <c r="C15" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="D15" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F15" s="4">
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="B16" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" s="4">
         <v>1</v>
@@ -1747,67 +1747,67 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="F21" s="4">
         <v>2</v>
@@ -1815,79 +1815,79 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>43</v>
+        <v>55</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>43</v>
+        <v>65</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>66</v>
+        <v>73</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26">
         <v>3</v>
@@ -1895,67 +1895,67 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="F30">
         <v>50</v>
@@ -1963,106 +1963,106 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>44</v>
+        <v>25</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="F37">
         <v>2</v>
@@ -2070,22 +2070,25 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>66</v>
+        <v>75</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>44</v>
+        <v>75</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B38" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="29100" windowHeight="12700"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -41,12 +41,18 @@
     <t>type</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>desc</t>
   </si>
   <si>
     <t>value</t>
   </si>
   <si>
+    <t>can_end_round</t>
+  </si>
+  <si>
     <t>阎王面具</t>
   </si>
   <si>
@@ -75,6 +81,9 @@
   </si>
   <si>
     <t>(array#sep=;),int</t>
+  </si>
+  <si>
+    <t>bool</t>
   </si>
   <si>
     <t>##group</t>
@@ -1327,15 +1336,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="4" width="32.8916666666667" customWidth="1"/>
-    <col min="5" max="5" width="64.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="15.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
+    <col min="3" max="4" width="32.8928571428571" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="64.3303571428571" customWidth="1"/>
+    <col min="6" max="6" width="15.1696428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,744 +1359,852 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:11">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:11">
+        <v>13</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" s="3" customFormat="1" spans="1:1">
       <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="B6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="L6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+    </row>
+    <row r="7" spans="2:12">
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>37</v>
+      </c>
+      <c r="G7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
       <c r="B8" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="G8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>45</v>
+      </c>
+      <c r="K8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
       <c r="B9" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="G9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" t="s">
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="K11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="B12" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="B13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F13" s="4">
         <v>100</v>
       </c>
-      <c r="H13" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="G13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="B14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D14" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="B15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-      <c r="J15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" t="s">
-        <v>69</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D21" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F21" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="2:6">
+      <c r="G21" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
       <c r="B22" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
+        <v>85</v>
+      </c>
+      <c r="G22" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="2:6">
+      <c r="G23" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
+        <v>87</v>
+      </c>
+      <c r="G24" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
       <c r="B25" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
+        <v>88</v>
+      </c>
+      <c r="G25" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
       <c r="B26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="D26" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="2:6">
+      <c r="G26" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
       <c r="B27" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6">
+        <v>90</v>
+      </c>
+      <c r="G27" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
       <c r="B28" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
+        <v>92</v>
+      </c>
+      <c r="G28" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
       <c r="B29" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>94</v>
+      </c>
+      <c r="G29" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
       <c r="B30" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F30">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" spans="2:6">
+      <c r="G30" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
       <c r="B31" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="C34" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
+        <v>98</v>
+      </c>
+      <c r="G34" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>44</v>
-      </c>
       <c r="D35" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
+        <v>99</v>
+      </c>
+      <c r="G35" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6">
+        <v>100</v>
+      </c>
+      <c r="G36" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
       <c r="B37" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F37">
         <v>2</v>
       </c>
-    </row>
-    <row r="38" spans="2:6">
+      <c r="G37" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
       <c r="B38" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F38">
         <v>2</v>
       </c>
+      <c r="G38" s="5" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B38" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="B1:B38">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
@@ -1337,12 +1337,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
-    <col min="3" max="4" width="32.8928571428571" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="64.3303571428571" customWidth="1"/>
-    <col min="6" max="6" width="15.1696428571429" customWidth="1"/>
+    <col min="2" max="2" width="32.8916666666667" customWidth="1"/>
+    <col min="3" max="4" width="32.8916666666667" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="64.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:12">
@@ -1421,12 +1421,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:1">
+    <row r="3" s="3" customFormat="1" spans="1:12">
       <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:5">
+    <row r="4" s="1" customFormat="1" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:12">
+    <row r="5" spans="1:12">
       <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>25</v>
@@ -1469,7 +1469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="1:12">
       <c r="B6" s="4" t="s">
         <v>29</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="1:12">
       <c r="B7" s="4" t="s">
         <v>35</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="1:12">
       <c r="B8" s="4" t="s">
         <v>40</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>42</v>
       </c>
       <c r="G8" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>43</v>
@@ -1571,7 +1571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="1:12">
       <c r="B9" s="4" t="s">
         <v>46</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>49</v>
@@ -1597,7 +1597,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="1:12">
       <c r="B10" s="4" t="s">
         <v>51</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>53</v>
       </c>
       <c r="G10" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>54</v>
@@ -1623,7 +1623,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="1:12">
       <c r="B11" s="4" t="s">
         <v>55</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="1:12">
       <c r="B12" s="4" t="s">
         <v>59</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="1:12">
       <c r="B13" s="4" t="s">
         <v>62</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="1:12">
       <c r="B14" s="4" t="s">
         <v>65</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="1:12">
       <c r="B15" s="4" t="s">
         <v>69</v>
       </c>
@@ -1741,13 +1741,13 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="1:12">
       <c r="B16" s="4" t="s">
         <v>73</v>
       </c>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="s">
         <v>76</v>
@@ -1797,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -1857,7 +1857,7 @@
         <v>83</v>
       </c>
       <c r="G20" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -1877,7 +1877,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -1897,7 +1897,7 @@
         <v>85</v>
       </c>
       <c r="G22" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -1952,7 +1952,7 @@
         <v>88</v>
       </c>
       <c r="G25" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -1972,7 +1972,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:7">
@@ -2032,7 +2032,7 @@
         <v>94</v>
       </c>
       <c r="G29" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:7">
@@ -2092,7 +2092,7 @@
         <v>96</v>
       </c>
       <c r="G32" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:7">
@@ -2109,7 +2109,7 @@
         <v>97</v>
       </c>
       <c r="G33" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -2126,7 +2126,7 @@
         <v>98</v>
       </c>
       <c r="G34" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -2143,7 +2143,7 @@
         <v>99</v>
       </c>
       <c r="G35" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -2160,7 +2160,7 @@
         <v>100</v>
       </c>
       <c r="G36" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:7">
@@ -2180,7 +2180,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="2:7">
@@ -2200,11 +2200,11 @@
         <v>2</v>
       </c>
       <c r="G38" s="5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B38">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B38" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>孟婆汤中的请神牌+1。</t>
+  </si>
+  <si>
+    <t>结束回合</t>
   </si>
 </sst>
 </file>
@@ -1336,12 +1339,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
     <col min="3" max="4" width="32.8928571428571" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="64.3303571428571" customWidth="1"/>
+    <col min="5" max="5" width="103.571428571429" customWidth="1"/>
     <col min="6" max="6" width="15.1696428571429" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2200,6 +2203,17 @@
         <v>2</v>
       </c>
       <c r="G38" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G39" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardTable!$B$1:$B$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardTable!$B$1:$B$39</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="127">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>type</t>
   </si>
   <si>
+    <t>intent</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
     <t>CardTypeEnum</t>
   </si>
   <si>
+    <t>IntentEnum</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
@@ -122,7 +128,7 @@
     <t>震慑</t>
   </si>
   <si>
-    <t>造成{0}点伤害，有{1}%的几率斩杀对手。打出后有{2}%的几率结束回合。</t>
+    <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。</t>
   </si>
   <si>
     <t>2;10;10</t>
@@ -212,7 +218,7 @@
     <t>养神</t>
   </si>
   <si>
-    <t>恢复{0}点生命。如果本回合中你打出过此牌的次数不小于{1}，有{2}%几率结束结束回合。</t>
+    <t>恢复{0}点生命。如果本回合中你打出过此牌的次数不小于{1}，有{2}%几率结束回合。</t>
   </si>
   <si>
     <t>2;2;100</t>
@@ -221,7 +227,7 @@
     <t>自力更生</t>
   </si>
   <si>
-    <t>视为打出本回合中你上一次打出的牌。打出后有{0}%几率结束结束回合。</t>
+    <t>视为打出本回合中你上一次打出的牌。打出后有{0}%几率结束回合。</t>
   </si>
   <si>
     <t>无常自力</t>
@@ -299,7 +305,7 @@
     <t>此牌无效。</t>
   </si>
   <si>
-    <t>造成{0}点伤害，有{1}%的几率斩杀对手。打出后有{2}%的几率结束回合。有{3}%的概率额外打出一次此牌。</t>
+    <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。有{3}%的概率额外打出一次此牌。</t>
   </si>
   <si>
     <t>2;10;10;50</t>
@@ -335,7 +341,76 @@
     <t>孟婆汤中的请神牌+1。</t>
   </si>
   <si>
-    <t>结束回合</t>
+    <t>拔舌鬼攻击</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，重复{1}次。打出后有{2}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>穷鬼吸血</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>对本我造成{0}点伤害，自己恢复{1}点生命。打出后有{2}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>铜柱鬼叠甲</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>铜柱鬼攻击</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害。打出后有{1}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>肉山鬼攻击</t>
+  </si>
+  <si>
+    <t>水鬼攻击</t>
+  </si>
+  <si>
+    <t>阎王攻击</t>
+  </si>
+  <si>
+    <t>阎王空过</t>
+  </si>
+  <si>
+    <t>喝咖啡</t>
+  </si>
+  <si>
+    <t>无事发生。打出后有{1}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>阎王叠甲</t>
+  </si>
+  <si>
+    <t>阎王减少死期</t>
+  </si>
+  <si>
+    <t>敌人的死期减少{0}。打出后有{1}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>阎王施加死期</t>
+  </si>
+  <si>
+    <t>敌人获得死期效果，倒计时为{0}。已有则无事发生。打出后有{1}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>黑白无常攻击</t>
+  </si>
+  <si>
+    <t>黑白无常打自己</t>
+  </si>
+  <si>
+    <t>对自己造成{0}点伤害。打出后有{1}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>黑白无常叠甲</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1073,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1015,6 +1090,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1339,16 +1417,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:M52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="32.8928571428571" customWidth="1"/>
-    <col min="3" max="4" width="32.8928571428571" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="103.571428571429" customWidth="1"/>
-    <col min="6" max="6" width="15.1696428571429" customWidth="1"/>
+    <col min="2" max="5" width="32.8916666666667" customWidth="1"/>
+    <col min="6" max="6" width="64.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="15.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1385,840 +1462,1065 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:1">
+        <v>14</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" s="3" customFormat="1" spans="1:13">
       <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:13">
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="4">
         <v>2</v>
       </c>
-      <c r="G5" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:13">
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="M6" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:13">
+      <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="M7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
+    </row>
+    <row r="8" customFormat="1" spans="1:13">
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>40</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="I8" t="s">
+      <c r="G8" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="H8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="J8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
+        <v>47</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:13">
       <c r="B9" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="F9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1</v>
+      </c>
+      <c r="H9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:13">
+      <c r="B10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="K9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>51</v>
-      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L10" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
+    </row>
+    <row r="11" customFormat="1" spans="1:13">
       <c r="B11" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="K11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
+      <c r="G11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="L11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:13">
       <c r="B12" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>59</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
+        <v>62</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:13">
       <c r="B13" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>62</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="4">
+        <v>64</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="4">
         <v>100</v>
       </c>
-      <c r="G13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11">
+      <c r="H13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:13">
       <c r="B14" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
         <v>68</v>
       </c>
-      <c r="K14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11">
+      <c r="G14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:13">
       <c r="B15" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>69</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="F15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:13">
+      <c r="B16" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="s">
+        <v>78</v>
+      </c>
+      <c r="J16" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="2:8">
+      <c r="B17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1</v>
+      </c>
+      <c r="H17" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="2:8">
+      <c r="B18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="2:8">
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="2:8">
+      <c r="B20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H20" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="2:8">
+      <c r="B21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="4">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="2:8">
+      <c r="B22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" spans="2:8">
+      <c r="B23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" spans="2:8">
+      <c r="B24" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="C24" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" spans="2:8">
+      <c r="B25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" spans="2:8">
+      <c r="B26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="2:8">
+      <c r="B27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" spans="2:8">
+      <c r="B28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" spans="2:8">
+      <c r="B29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="2:8">
+      <c r="B30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G30">
+        <v>50</v>
+      </c>
+      <c r="H30" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="2:8">
+      <c r="B31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="2:8">
+      <c r="B32" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H32" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="2:8">
+      <c r="B33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H33" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="2:8">
+      <c r="B34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" customFormat="1" spans="2:8">
+      <c r="B35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H35" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="2:8">
+      <c r="B36" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" t="s">
-        <v>77</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="C36" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="5" t="s">
+      <c r="D36" s="6"/>
+      <c r="E36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H36" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="2:8">
+      <c r="B37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="D37" s="6"/>
+      <c r="E37" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="2:8">
+      <c r="B38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38">
+        <v>2</v>
+      </c>
+      <c r="H38" s="5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="4">
-        <v>2</v>
-      </c>
-      <c r="G21" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="5" t="s">
+      <c r="F39" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H39" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="H40" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="H41" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H43" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H44" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H45" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="H46" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="G25" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="G29" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30">
-        <v>50</v>
-      </c>
-      <c r="G30" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G31" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G32" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G34" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G35" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G36" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37">
-        <v>2</v>
-      </c>
-      <c r="G37" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38">
-        <v>2</v>
-      </c>
-      <c r="G38" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" t="s">
-        <v>101</v>
-      </c>
-      <c r="E39" t="s">
-        <v>101</v>
-      </c>
-      <c r="G39" t="b">
+      <c r="H47" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H48" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H49" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H50" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H51" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H52" s="5" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B38">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B39" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="29100" windowHeight="12700"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardTable!$B$1:$B$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardTable!$B$1:$B$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="128">
   <si>
     <t>##var</t>
   </si>
@@ -56,72 +56,75 @@
     <t>can_end_round</t>
   </si>
   <si>
+    <t>mask_to_card_effect</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>CardEnum</t>
+  </si>
+  <si>
+    <t>CardTypeEnum</t>
+  </si>
+  <si>
+    <t>IntentEnum</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=;),int</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>map,MaskEnum,CardEnum</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>卡牌名</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>轻击</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害。</t>
+  </si>
+  <si>
     <t>阎王面具</t>
   </si>
   <si>
+    <t>阎王轻击</t>
+  </si>
+  <si>
     <t>无常面具</t>
   </si>
   <si>
-    <t>阎罗面具</t>
+    <t>无常轻击</t>
   </si>
   <si>
     <t>孟婆面具</t>
   </si>
   <si>
+    <t>孟婆熬药攻击</t>
+  </si>
+  <si>
     <t>二郎神面具</t>
   </si>
   <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>CardEnum</t>
-  </si>
-  <si>
-    <t>CardTypeEnum</t>
-  </si>
-  <si>
-    <t>IntentEnum</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>(array#sep=;),int</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>卡牌名</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>轻击</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害。</t>
-  </si>
-  <si>
-    <t>阎王轻击</t>
-  </si>
-  <si>
-    <t>无常轻击</t>
-  </si>
-  <si>
-    <t>孟婆熬药攻击</t>
-  </si>
-  <si>
     <t>二郎神攻击</t>
   </si>
   <si>
@@ -134,211 +137,211 @@
     <t>2;10;10</t>
   </si>
   <si>
+    <t>万我</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>1;0;1;100</t>
+  </si>
+  <si>
+    <t>吸魂</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。</t>
+  </si>
+  <si>
+    <t>1;5</t>
+  </si>
+  <si>
+    <t>炼魂</t>
+  </si>
+  <si>
+    <t>功能</t>
+  </si>
+  <si>
+    <t>获得{0}点护甲。</t>
+  </si>
+  <si>
+    <t>慷慨</t>
+  </si>
+  <si>
+    <t>受到{0}点伤害，然后摸{1}张牌。</t>
+  </si>
+  <si>
+    <t>2;2</t>
+  </si>
+  <si>
+    <t>静心</t>
+  </si>
+  <si>
+    <t>获得{0}点护甲。打出后有{1}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>3;100</t>
+  </si>
+  <si>
+    <t>养神</t>
+  </si>
+  <si>
+    <t>恢复{0}点生命。如果本回合中你打出过此牌的次数不小于{1}，有{2}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>2;2;100</t>
+  </si>
+  <si>
+    <t>自力更生</t>
+  </si>
+  <si>
+    <t>视为打出本回合中你上一次打出的牌。打出后有{0}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>碎魂</t>
+  </si>
+  <si>
+    <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>2;0;100</t>
+  </si>
+  <si>
+    <t>壮魂</t>
+  </si>
+  <si>
+    <t>请神</t>
+  </si>
+  <si>
+    <t>直到你的下个回合结束时，当你造成伤害时，你获得{0}点护甲。</t>
+  </si>
+  <si>
+    <t>傩戏开场</t>
+  </si>
+  <si>
+    <t>傩戏开场！</t>
+  </si>
+  <si>
+    <t>直到你的回合结束时，随机佩戴一个面具（从十殿阎罗、孟婆、二郎真君中随机选择）。</t>
+  </si>
+  <si>
     <t>阎王震慑</t>
   </si>
   <si>
+    <t>2;20;10</t>
+  </si>
+  <si>
+    <t>阎王万我</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
+  </si>
+  <si>
+    <t>1;0;1;100;5;1</t>
+  </si>
+  <si>
+    <t>阎王吸魂</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，获得{1}点护甲。</t>
+  </si>
+  <si>
+    <t>1;2</t>
+  </si>
+  <si>
+    <t>阎王炼魂</t>
+  </si>
+  <si>
+    <t>阎王慷慨</t>
+  </si>
+  <si>
+    <t>获得{0}点护甲，然后摸{1}张牌。</t>
+  </si>
+  <si>
+    <t>1;1</t>
+  </si>
+  <si>
+    <t>阎王静心</t>
+  </si>
+  <si>
+    <t>阎王碎魂</t>
+  </si>
+  <si>
+    <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。敌人的死期减少{3}。</t>
+  </si>
+  <si>
+    <t>2;0;100;1</t>
+  </si>
+  <si>
+    <t>面具傩戏</t>
+  </si>
+  <si>
+    <t>此牌无效。</t>
+  </si>
+  <si>
     <t>无常震慑</t>
   </si>
   <si>
+    <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。有{3}%的概率额外打出一次此牌。</t>
+  </si>
+  <si>
+    <t>2;10;10;50</t>
+  </si>
+  <si>
+    <t>无常万我</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
+  </si>
+  <si>
+    <t>1;0;50;3;1;100</t>
+  </si>
+  <si>
+    <t>无常吸魂</t>
+  </si>
+  <si>
+    <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。有{2}%的概率额外打出一次此牌。</t>
+  </si>
+  <si>
+    <t>1;5;50</t>
+  </si>
+  <si>
+    <t>无常自力</t>
+  </si>
+  <si>
     <t>阎罗震慑</t>
   </si>
   <si>
-    <t>万我</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。</t>
-  </si>
-  <si>
-    <t>1;0;1;100</t>
-  </si>
-  <si>
-    <t>阎王万我</t>
-  </si>
-  <si>
-    <t>无常万我</t>
-  </si>
-  <si>
-    <t>吸魂</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。</t>
-  </si>
-  <si>
-    <t>1;5</t>
-  </si>
-  <si>
-    <t>阎王吸魂</t>
-  </si>
-  <si>
-    <t>无常吸魂</t>
+    <t>2;30;30</t>
   </si>
   <si>
     <t>阎罗吸魂</t>
   </si>
   <si>
-    <t>炼魂</t>
-  </si>
-  <si>
-    <t>功能</t>
-  </si>
-  <si>
-    <t>获得{0}点护甲。</t>
-  </si>
-  <si>
-    <t>阎王炼魂</t>
+    <t>3;3</t>
+  </si>
+  <si>
+    <t>阎罗傩戏</t>
+  </si>
+  <si>
+    <t>随机切换一个律令（可能重复）。</t>
+  </si>
+  <si>
+    <t>孟婆汤中的攻击牌+1。</t>
   </si>
   <si>
     <t>孟婆熬药功能</t>
   </si>
   <si>
-    <t>慷慨</t>
-  </si>
-  <si>
-    <t>受到{0}点伤害，然后摸{1}张牌。</t>
-  </si>
-  <si>
-    <t>2;2</t>
-  </si>
-  <si>
-    <t>阎王慷慨</t>
-  </si>
-  <si>
-    <t>静心</t>
-  </si>
-  <si>
-    <t>获得{0}点护甲。打出后有{1}%几率结束回合。</t>
-  </si>
-  <si>
-    <t>3;100</t>
-  </si>
-  <si>
-    <t>阎王静心</t>
-  </si>
-  <si>
-    <t>养神</t>
-  </si>
-  <si>
-    <t>恢复{0}点生命。如果本回合中你打出过此牌的次数不小于{1}，有{2}%几率结束回合。</t>
-  </si>
-  <si>
-    <t>2;2;100</t>
-  </si>
-  <si>
-    <t>自力更生</t>
-  </si>
-  <si>
-    <t>视为打出本回合中你上一次打出的牌。打出后有{0}%几率结束回合。</t>
-  </si>
-  <si>
-    <t>无常自力</t>
-  </si>
-  <si>
-    <t>碎魂</t>
-  </si>
-  <si>
-    <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。</t>
-  </si>
-  <si>
-    <t>2;0;100</t>
-  </si>
-  <si>
-    <t>阎王碎魂</t>
-  </si>
-  <si>
-    <t>壮魂</t>
-  </si>
-  <si>
-    <t>请神</t>
-  </si>
-  <si>
-    <t>直到你的下个回合结束时，当你造成伤害时，你获得{0}点护甲。</t>
+    <t>孟婆汤中的功能牌+1。</t>
   </si>
   <si>
     <t>孟婆熬药请神</t>
   </si>
   <si>
-    <t>傩戏开场</t>
-  </si>
-  <si>
-    <t>傩戏开场！</t>
-  </si>
-  <si>
-    <t>直到你的回合结束时，随机佩戴一个面具（从十殿阎罗、孟婆、二郎真君中随机选择）。</t>
-  </si>
-  <si>
-    <t>面具傩戏</t>
-  </si>
-  <si>
-    <t>阎罗傩戏</t>
+    <t>孟婆汤中的请神牌+1。</t>
   </si>
   <si>
     <t>二郎神请神</t>
-  </si>
-  <si>
-    <t>2;20;10</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
-  </si>
-  <si>
-    <t>1;0;1;100;5;1</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害，获得{1}点护甲。</t>
-  </si>
-  <si>
-    <t>1;2</t>
-  </si>
-  <si>
-    <t>获得{0}点护甲，然后摸{1}张牌。</t>
-  </si>
-  <si>
-    <t>1;1</t>
-  </si>
-  <si>
-    <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。敌人的死期减少{3}。</t>
-  </si>
-  <si>
-    <t>2;0;100;1</t>
-  </si>
-  <si>
-    <t>此牌无效。</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。有{3}%的概率额外打出一次此牌。</t>
-  </si>
-  <si>
-    <t>2;10;10;50</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
-  </si>
-  <si>
-    <t>1;0;50;3;1;100</t>
-  </si>
-  <si>
-    <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。有{2}%的概率额外打出一次此牌。</t>
-  </si>
-  <si>
-    <t>1;5;50</t>
-  </si>
-  <si>
-    <t>2;30;30</t>
-  </si>
-  <si>
-    <t>3;3</t>
-  </si>
-  <si>
-    <t>随机切换一个律令（可能重复）。</t>
-  </si>
-  <si>
-    <t>孟婆汤中的攻击牌+1。</t>
-  </si>
-  <si>
-    <t>孟婆汤中的功能牌+1。</t>
-  </si>
-  <si>
-    <t>孟婆汤中的请神牌+1。</t>
   </si>
   <si>
     <t>拔舌鬼攻击</t>
@@ -1073,7 +1076,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1095,7 +1098,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1417,15 +1435,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:Q52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="5" width="32.8916666666667" customWidth="1"/>
-    <col min="6" max="6" width="64.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="15.1666666666667" customWidth="1"/>
+    <col min="2" max="5" width="32.8928571428571" customWidth="1"/>
+    <col min="6" max="6" width="64.3303571428571" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1696428571429" customWidth="1"/>
+    <col min="9" max="9" width="12.0446428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1450,92 +1469,93 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="10"/>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:17">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="I2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+      <c r="Q2" s="11"/>
+    </row>
+    <row r="3" s="3" customFormat="1" spans="1:17">
+      <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="12"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:13">
-      <c r="A4" s="1" t="s">
+    <row r="5" customFormat="1" spans="2:16">
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" spans="1:13">
-      <c r="B5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G5" s="4">
         <v>2</v>
@@ -1543,137 +1563,113 @@
       <c r="H5" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
         <v>27</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>28</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="O5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:13">
+      <c r="P5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="2:10">
       <c r="B6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H6" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" t="s">
+      <c r="I6"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" customFormat="1" spans="2:10">
+      <c r="B7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:13">
-      <c r="B7" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="H7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" customFormat="1" spans="2:10">
+      <c r="B8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="J7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" spans="1:13">
-      <c r="B8" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H8" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="1:13">
+      <c r="I8"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" customFormat="1" spans="2:10">
       <c r="B9" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G9" s="4">
         <v>1</v>
@@ -1681,104 +1677,89 @@
       <c r="H9" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" spans="1:13">
+      <c r="I9"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" customFormat="1" spans="2:10">
       <c r="B10" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H10" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="L10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:13">
+      <c r="I10"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" customFormat="1" spans="2:10">
       <c r="B11" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="H11" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:13">
+      <c r="I11"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" customFormat="1" spans="2:8">
       <c r="B12" s="4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H12" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="L12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:13">
+    </row>
+    <row r="13" customFormat="1" spans="2:8">
       <c r="B13" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G13" s="4">
         <v>100</v>
@@ -1786,53 +1767,41 @@
       <c r="H13" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="J13" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:13">
+    </row>
+    <row r="14" customFormat="1" spans="2:8">
       <c r="B14" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H14" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="I14" t="s">
-        <v>70</v>
-      </c>
-      <c r="L14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:13">
+    </row>
+    <row r="15" customFormat="1" spans="2:8">
       <c r="B15" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="G15" s="4">
         <v>1</v>
@@ -1840,57 +1809,39 @@
       <c r="H15" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="L15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:13">
+    </row>
+    <row r="16" customFormat="1" spans="2:8">
       <c r="B16" s="4" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="I16" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" t="s">
-        <v>78</v>
-      </c>
-      <c r="K16" t="s">
-        <v>79</v>
-      </c>
-      <c r="L16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M16" s="6" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="17" customFormat="1" spans="2:8">
       <c r="B17" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G17" s="4">
         <v>1</v>
@@ -1901,20 +1852,20 @@
     </row>
     <row r="18" customFormat="1" spans="2:8">
       <c r="B18" s="5" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="H18" s="5" t="b">
         <v>1</v>
@@ -1922,20 +1873,20 @@
     </row>
     <row r="19" customFormat="1" spans="2:8">
       <c r="B19" s="5" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="H19" s="5" t="b">
         <v>1</v>
@@ -1943,20 +1894,20 @@
     </row>
     <row r="20" customFormat="1" spans="2:8">
       <c r="B20" s="5" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="H20" s="5" t="b">
         <v>0</v>
@@ -1964,17 +1915,17 @@
     </row>
     <row r="21" customFormat="1" spans="2:8">
       <c r="B21" s="5" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G21" s="4">
         <v>2</v>
@@ -1985,20 +1936,20 @@
     </row>
     <row r="22" customFormat="1" spans="2:8">
       <c r="B22" s="5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H22" s="5" t="b">
         <v>0</v>
@@ -2006,17 +1957,17 @@
     </row>
     <row r="23" customFormat="1" spans="2:8">
       <c r="B23" s="5" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="5" t="b">
@@ -2025,20 +1976,20 @@
     </row>
     <row r="24" customFormat="1" spans="2:8">
       <c r="B24" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H24" s="5" t="b">
         <v>1</v>
@@ -2046,17 +1997,17 @@
     </row>
     <row r="25" customFormat="1" spans="2:8">
       <c r="B25" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H25" s="5" t="b">
         <v>0</v>
@@ -2064,17 +2015,17 @@
     </row>
     <row r="26" customFormat="1" spans="2:8">
       <c r="B26" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G26">
         <v>3</v>
@@ -2085,20 +2036,20 @@
     </row>
     <row r="27" customFormat="1" spans="2:8">
       <c r="B27" s="6" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H27" s="5" t="b">
         <v>1</v>
@@ -2106,20 +2057,20 @@
     </row>
     <row r="28" customFormat="1" spans="2:8">
       <c r="B28" s="6" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G28" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H28" s="5" t="b">
         <v>1</v>
@@ -2127,20 +2078,20 @@
     </row>
     <row r="29" customFormat="1" spans="2:8">
       <c r="B29" s="6" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H29" s="5" t="b">
         <v>0</v>
@@ -2148,17 +2099,17 @@
     </row>
     <row r="30" customFormat="1" spans="2:8">
       <c r="B30" s="6" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G30">
         <v>50</v>
@@ -2169,20 +2120,20 @@
     </row>
     <row r="31" customFormat="1" spans="2:8">
       <c r="B31" s="6" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H31" s="5" t="b">
         <v>1</v>
@@ -2190,20 +2141,20 @@
     </row>
     <row r="32" customFormat="1" spans="2:8">
       <c r="B32" s="6" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H32" s="5" t="b">
         <v>0</v>
@@ -2211,17 +2162,17 @@
     </row>
     <row r="33" customFormat="1" spans="2:8">
       <c r="B33" s="6" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H33" s="5" t="b">
         <v>0</v>
@@ -2232,14 +2183,14 @@
         <v>29</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H34" s="5" t="b">
         <v>0</v>
@@ -2247,17 +2198,17 @@
     </row>
     <row r="35" customFormat="1" spans="2:8">
       <c r="B35" s="6" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H35" s="5" t="b">
         <v>0</v>
@@ -2265,14 +2216,14 @@
     </row>
     <row r="36" customFormat="1" spans="2:8">
       <c r="B36" s="6" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>102</v>
@@ -2283,17 +2234,17 @@
     </row>
     <row r="37" customFormat="1" spans="2:8">
       <c r="B37" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2304,17 +2255,17 @@
     </row>
     <row r="38" customFormat="1" spans="2:8">
       <c r="B38" s="6" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -2325,13 +2276,13 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>104</v>
+        <v>22</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="H39" s="5" t="b">
         <v>1</v>
@@ -2339,13 +2290,13 @@
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F40" s="7" t="s">
         <v>107</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="H40" s="5" t="b">
         <v>1</v>
@@ -2353,13 +2304,13 @@
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>58</v>
+        <v>110</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="H41" s="5" t="b">
         <v>1</v>
@@ -2367,13 +2318,13 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>111</v>
+        <v>22</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="H42" s="5" t="b">
         <v>1</v>
@@ -2381,13 +2332,13 @@
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>111</v>
       </c>
       <c r="H43" s="5" t="b">
         <v>1</v>
@@ -2395,13 +2346,13 @@
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>111</v>
+        <v>22</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="H44" s="5" t="b">
         <v>1</v>
@@ -2409,13 +2360,13 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>111</v>
+        <v>22</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="H45" s="5" t="b">
         <v>1</v>
@@ -2423,13 +2374,13 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F46" s="7" t="s">
         <v>117</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="H46" s="5" t="b">
         <v>1</v>
@@ -2437,13 +2388,13 @@
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>58</v>
+        <v>110</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="H47" s="5" t="b">
         <v>1</v>
@@ -2451,13 +2402,13 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>120</v>
+        <v>117</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="H48" s="5" t="b">
         <v>1</v>
@@ -2465,13 +2416,13 @@
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>122</v>
+        <v>117</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="H49" s="5" t="b">
         <v>1</v>
@@ -2479,13 +2430,13 @@
     </row>
     <row r="50" spans="2:8">
       <c r="B50" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>111</v>
+        <v>22</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="H50" s="5" t="b">
         <v>1</v>
@@ -2493,13 +2444,13 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>125</v>
+        <v>22</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="H51" s="5" t="b">
         <v>1</v>
@@ -2507,22 +2458,27 @@
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>58</v>
+        <v>110</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="H52" s="5" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B39" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="B1:B52">
     <extLst/>
   </autoFilter>
+  <mergeCells count="3">
+    <mergeCell ref="I1:P1"/>
+    <mergeCell ref="I2:P2"/>
+    <mergeCell ref="I3:P3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -137,6 +137,18 @@
     <t>2;10;10</t>
   </si>
   <si>
+    <t>阎王震慑</t>
+  </si>
+  <si>
+    <t>无常震慑</t>
+  </si>
+  <si>
+    <t>阎罗面具</t>
+  </si>
+  <si>
+    <t>阎罗震慑</t>
+  </si>
+  <si>
     <t>万我</t>
   </si>
   <si>
@@ -146,6 +158,12 @@
     <t>1;0;1;100</t>
   </si>
   <si>
+    <t>阎王万我</t>
+  </si>
+  <si>
+    <t>无常万我</t>
+  </si>
+  <si>
     <t>吸魂</t>
   </si>
   <si>
@@ -155,6 +173,15 @@
     <t>1;5</t>
   </si>
   <si>
+    <t>阎王吸魂</t>
+  </si>
+  <si>
+    <t>无常吸魂</t>
+  </si>
+  <si>
+    <t>阎罗吸魂</t>
+  </si>
+  <si>
     <t>炼魂</t>
   </si>
   <si>
@@ -164,6 +191,12 @@
     <t>获得{0}点护甲。</t>
   </si>
   <si>
+    <t>阎王炼魂</t>
+  </si>
+  <si>
+    <t>孟婆熬药功能</t>
+  </si>
+  <si>
     <t>慷慨</t>
   </si>
   <si>
@@ -173,6 +206,9 @@
     <t>2;2</t>
   </si>
   <si>
+    <t>阎王慷慨</t>
+  </si>
+  <si>
     <t>静心</t>
   </si>
   <si>
@@ -182,6 +218,9 @@
     <t>3;100</t>
   </si>
   <si>
+    <t>阎王静心</t>
+  </si>
+  <si>
     <t>养神</t>
   </si>
   <si>
@@ -197,6 +236,9 @@
     <t>视为打出本回合中你上一次打出的牌。打出后有{0}%几率结束回合。</t>
   </si>
   <si>
+    <t>无常自力</t>
+  </si>
+  <si>
     <t>碎魂</t>
   </si>
   <si>
@@ -206,6 +248,9 @@
     <t>2;0;100</t>
   </si>
   <si>
+    <t>阎王碎魂</t>
+  </si>
+  <si>
     <t>壮魂</t>
   </si>
   <si>
@@ -215,6 +260,9 @@
     <t>直到你的下个回合结束时，当你造成伤害时，你获得{0}点护甲。</t>
   </si>
   <si>
+    <t>孟婆熬药请神</t>
+  </si>
+  <si>
     <t>傩戏开场</t>
   </si>
   <si>
@@ -224,132 +272,90 @@
     <t>直到你的回合结束时，随机佩戴一个面具（从十殿阎罗、孟婆、二郎真君中随机选择）。</t>
   </si>
   <si>
-    <t>阎王震慑</t>
+    <t>面具傩戏</t>
+  </si>
+  <si>
+    <t>阎罗傩戏</t>
+  </si>
+  <si>
+    <t>二郎神请神</t>
   </si>
   <si>
     <t>2;20;10</t>
   </si>
   <si>
-    <t>阎王万我</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
   </si>
   <si>
     <t>1;0;1;100;5;1</t>
   </si>
   <si>
-    <t>阎王吸魂</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，获得{1}点护甲。</t>
   </si>
   <si>
     <t>1;2</t>
   </si>
   <si>
-    <t>阎王炼魂</t>
-  </si>
-  <si>
-    <t>阎王慷慨</t>
-  </si>
-  <si>
     <t>获得{0}点护甲，然后摸{1}张牌。</t>
   </si>
   <si>
     <t>1;1</t>
   </si>
   <si>
-    <t>阎王静心</t>
-  </si>
-  <si>
-    <t>阎王碎魂</t>
-  </si>
-  <si>
     <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。敌人的死期减少{3}。</t>
   </si>
   <si>
     <t>2;0;100;1</t>
   </si>
   <si>
-    <t>面具傩戏</t>
-  </si>
-  <si>
     <t>此牌无效。</t>
   </si>
   <si>
-    <t>无常震慑</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。有{3}%的概率额外打出一次此牌。</t>
   </si>
   <si>
     <t>2;10;10;50</t>
   </si>
   <si>
-    <t>无常万我</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
   </si>
   <si>
     <t>1;0;50;3;1;100</t>
   </si>
   <si>
-    <t>无常吸魂</t>
-  </si>
-  <si>
     <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。有{2}%的概率额外打出一次此牌。</t>
   </si>
   <si>
     <t>1;5;50</t>
   </si>
   <si>
-    <t>无常自力</t>
-  </si>
-  <si>
-    <t>阎罗震慑</t>
-  </si>
-  <si>
     <t>2;30;30</t>
   </si>
   <si>
-    <t>阎罗吸魂</t>
-  </si>
-  <si>
     <t>3;3</t>
   </si>
   <si>
-    <t>阎罗傩戏</t>
-  </si>
-  <si>
     <t>随机切换一个律令（可能重复）。</t>
   </si>
   <si>
     <t>孟婆汤中的攻击牌+1。</t>
   </si>
   <si>
-    <t>孟婆熬药功能</t>
-  </si>
-  <si>
     <t>孟婆汤中的功能牌+1。</t>
   </si>
   <si>
-    <t>孟婆熬药请神</t>
-  </si>
-  <si>
     <t>孟婆汤中的请神牌+1。</t>
   </si>
   <si>
-    <t>二郎神请神</t>
-  </si>
-  <si>
     <t>拔舌鬼攻击</t>
   </si>
   <si>
     <t>造成{0}点伤害，重复{1}次。打出后有{2}%几率结束回合。</t>
   </si>
   <si>
+    <t>1;1;100</t>
+  </si>
+  <si>
     <t>穷鬼吸血</t>
   </si>
   <si>
@@ -365,28 +371,40 @@
     <t>防御</t>
   </si>
   <si>
+    <t>5;100</t>
+  </si>
+  <si>
     <t>铜柱鬼攻击</t>
   </si>
   <si>
     <t>造成{0}点伤害。打出后有{1}%几率结束回合。</t>
   </si>
   <si>
+    <t>10;100</t>
+  </si>
+  <si>
     <t>肉山鬼攻击</t>
   </si>
   <si>
     <t>水鬼攻击</t>
   </si>
   <si>
+    <t>1;100</t>
+  </si>
+  <si>
     <t>阎王攻击</t>
   </si>
   <si>
+    <t>2;100</t>
+  </si>
+  <si>
     <t>阎王空过</t>
   </si>
   <si>
     <t>喝咖啡</t>
   </si>
   <si>
-    <t>无事发生。打出后有{1}%几率结束回合。</t>
+    <t>无事发生。打出后有{0}%几率结束回合。</t>
   </si>
   <si>
     <t>阎王叠甲</t>
@@ -1076,7 +1094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1087,33 +1105,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1435,16 +1456,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:R52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="5" width="32.8928571428571" customWidth="1"/>
-    <col min="6" max="6" width="64.3303571428571" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1696428571429" customWidth="1"/>
-    <col min="9" max="9" width="12.0446428571429" customWidth="1"/>
+    <col min="2" max="5" width="32.8916666666667" customWidth="1"/>
+    <col min="6" max="6" width="64.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="15.1666666666667" customWidth="1"/>
+    <col min="9" max="9" width="12.0416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1469,19 +1490,19 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="10"/>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:17">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1506,33 +1527,33 @@
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="11"/>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:17">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="7"/>
+    </row>
+    <row r="3" s="3" customFormat="1" spans="1:18">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="12"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="9"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:18">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1543,935 +1564,1251 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:16">
-      <c r="B5" s="4" t="s">
+    <row r="5" customFormat="1" spans="1:18">
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="10">
         <v>2</v>
       </c>
-      <c r="H5" s="5" t="b">
+      <c r="H5" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:10">
-      <c r="B6" s="4" t="s">
+    <row r="6" customFormat="1" spans="1:18">
+      <c r="B6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6"/>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" customFormat="1" spans="2:10">
-      <c r="B7" s="4" t="s">
+      <c r="H6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="K6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:18">
+      <c r="B7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:18">
+      <c r="B8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:18">
+      <c r="B9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R9" s="13"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:18">
+      <c r="B10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" s="13"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:18">
+      <c r="B11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R11" s="13"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:18">
+      <c r="B12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="12"/>
+      <c r="J12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R12" s="13"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:18">
+      <c r="B13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="10">
+        <v>100</v>
+      </c>
+      <c r="H13" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="12"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R13" s="13"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:18">
+      <c r="B14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R14" s="13"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:18">
+      <c r="B15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12"/>
+      <c r="J15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="R15" s="13"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:18">
+      <c r="B16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="2:14">
+      <c r="B17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="2:14">
+      <c r="B18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" customFormat="1" spans="2:10">
-      <c r="B8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="C18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="5" t="b">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="2:14">
+      <c r="B19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="2:14">
+      <c r="B20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="I8"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" customFormat="1" spans="2:10">
-      <c r="B9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="b">
+      <c r="J20" s="11"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" customFormat="1" spans="2:14">
+      <c r="B21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="10">
+        <v>2</v>
+      </c>
+      <c r="H21" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="I9"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" customFormat="1" spans="2:10">
-      <c r="B10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="5" t="b">
+      <c r="J21" s="11"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+    </row>
+    <row r="22" customFormat="1" spans="2:14">
+      <c r="B22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="I10"/>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" customFormat="1" spans="2:10">
-      <c r="B11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11"/>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12" customFormat="1" spans="2:8">
-      <c r="B12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="J22" s="11"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+    </row>
+    <row r="23" customFormat="1" spans="2:14">
+      <c r="B23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="2:8">
-      <c r="B13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="4">
-        <v>100</v>
-      </c>
-      <c r="H13" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="2:8">
-      <c r="B14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="2:8">
-      <c r="B15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="b">
+      <c r="G23" s="10"/>
+      <c r="H23" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+    </row>
+    <row r="24" customFormat="1" spans="2:14">
+      <c r="B24" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" s="11"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" customFormat="1" spans="2:14">
+      <c r="B25" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customFormat="1" spans="2:8">
-      <c r="B16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="2:8">
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="J25" s="11"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="13"/>
+    </row>
+    <row r="26" customFormat="1" spans="2:14">
+      <c r="B26" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="4">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="2:8">
-      <c r="B18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" spans="2:8">
-      <c r="B19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="2:8">
-      <c r="B20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="2:8">
-      <c r="B21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="4">
-        <v>2</v>
-      </c>
-      <c r="H21" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="2:8">
-      <c r="B22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="2:8">
-      <c r="B23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="2:8">
-      <c r="B24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="2:8">
-      <c r="B25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H25" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="2:8">
-      <c r="B26" s="6" t="s">
+      <c r="D26" s="12"/>
+      <c r="E26" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G26">
         <v>3</v>
       </c>
-      <c r="H26" s="5" t="b">
+      <c r="H26" s="11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customFormat="1" spans="2:8">
-      <c r="B27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="J26" s="11"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" customFormat="1" spans="2:14">
+      <c r="B27" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="2:8">
-      <c r="B28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="D27" s="12"/>
+      <c r="E27" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="13"/>
+    </row>
+    <row r="28" customFormat="1" spans="2:14">
+      <c r="B28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>86</v>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
-      </c>
-      <c r="H28" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="2:8">
-      <c r="B29" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="13"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="13"/>
+    </row>
+    <row r="29" customFormat="1" spans="2:14">
+      <c r="B29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="5" t="b">
+      <c r="D29" s="12"/>
+      <c r="E29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" customFormat="1" spans="2:8">
-      <c r="B30" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>54</v>
+      <c r="J29" s="12"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="13"/>
+    </row>
+    <row r="30" customFormat="1" spans="2:14">
+      <c r="B30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="G30">
         <v>50</v>
       </c>
-      <c r="H30" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="2:8">
-      <c r="B31" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="H30" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="13"/>
+    </row>
+    <row r="31" customFormat="1" spans="2:14">
+      <c r="B31" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="D31" s="12"/>
+      <c r="E31" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="2:8">
-      <c r="B32" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="G31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H31" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+    </row>
+    <row r="32" customFormat="1" spans="2:14">
+      <c r="B32" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H32" s="5" t="b">
+      <c r="D32" s="12"/>
+      <c r="E32" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H32" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:8">
-      <c r="B33" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H33" s="5" t="b">
+      <c r="B33" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H33" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="2:8">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="12"/>
+      <c r="E34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H34" s="5" t="b">
+      <c r="F34" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="2:8">
-      <c r="B35" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="5" t="b">
+      <c r="B35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="2:8">
-      <c r="B36" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H36" s="5" t="b">
+      <c r="B36" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="2:8">
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="s">
+      <c r="D37" s="12"/>
+      <c r="E37" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>43</v>
+      <c r="F37" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="G37">
         <v>2</v>
       </c>
-      <c r="H37" s="5" t="b">
+      <c r="H37" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="2:8">
-      <c r="B38" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>43</v>
+      <c r="B38" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
-      <c r="H38" s="5" t="b">
+      <c r="H38" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="B39" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="5" t="b">
+      <c r="F39" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39" t="s">
+        <v>107</v>
+      </c>
+      <c r="H39" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="6" t="s">
+      <c r="B40" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H40" s="5" t="b">
+      <c r="H40" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H41" s="5" t="b">
+      <c r="B41" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" s="6" t="s">
+      <c r="B42" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G42" t="s">
+        <v>116</v>
+      </c>
+      <c r="H42" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H42" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="6" t="s">
+      <c r="F47" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47" t="s">
+        <v>116</v>
+      </c>
+      <c r="H47" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" t="s">
+        <v>119</v>
+      </c>
+      <c r="H48" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" t="s">
         <v>113</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="H49" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F50" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G51" t="s">
+        <v>121</v>
+      </c>
+      <c r="H51" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H43" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H44" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H45" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H46" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H47" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H48" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="H49" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="H51" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H52" s="5" t="b">
+      <c r="F52" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G52" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="11" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B52">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B52" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="3">

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="12700"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="135">
   <si>
     <t>##var</t>
   </si>
@@ -137,6 +137,18 @@
     <t>2;10;10</t>
   </si>
   <si>
+    <t>阎王震慑</t>
+  </si>
+  <si>
+    <t>无常震慑</t>
+  </si>
+  <si>
+    <t>阎罗面具</t>
+  </si>
+  <si>
+    <t>阎罗震慑</t>
+  </si>
+  <si>
     <t>万我</t>
   </si>
   <si>
@@ -146,6 +158,12 @@
     <t>1;0;1;100</t>
   </si>
   <si>
+    <t>阎王万我</t>
+  </si>
+  <si>
+    <t>无常万我</t>
+  </si>
+  <si>
     <t>吸魂</t>
   </si>
   <si>
@@ -155,6 +173,15 @@
     <t>1;5</t>
   </si>
   <si>
+    <t>阎王吸魂</t>
+  </si>
+  <si>
+    <t>无常吸魂</t>
+  </si>
+  <si>
+    <t>阎罗吸魂</t>
+  </si>
+  <si>
     <t>炼魂</t>
   </si>
   <si>
@@ -164,6 +191,12 @@
     <t>获得{0}点护甲。</t>
   </si>
   <si>
+    <t>阎王炼魂</t>
+  </si>
+  <si>
+    <t>孟婆熬药功能</t>
+  </si>
+  <si>
     <t>慷慨</t>
   </si>
   <si>
@@ -173,6 +206,9 @@
     <t>2;2</t>
   </si>
   <si>
+    <t>阎王慷慨</t>
+  </si>
+  <si>
     <t>静心</t>
   </si>
   <si>
@@ -182,6 +218,9 @@
     <t>3;100</t>
   </si>
   <si>
+    <t>阎王静心</t>
+  </si>
+  <si>
     <t>养神</t>
   </si>
   <si>
@@ -197,6 +236,9 @@
     <t>视为打出本回合中你上一次打出的牌。打出后有{0}%几率结束回合。</t>
   </si>
   <si>
+    <t>无常自力</t>
+  </si>
+  <si>
     <t>碎魂</t>
   </si>
   <si>
@@ -206,6 +248,9 @@
     <t>2;0;100</t>
   </si>
   <si>
+    <t>阎王碎魂</t>
+  </si>
+  <si>
     <t>壮魂</t>
   </si>
   <si>
@@ -215,6 +260,9 @@
     <t>直到你的下个回合结束时，当你造成伤害时，你获得{0}点护甲。</t>
   </si>
   <si>
+    <t>孟婆熬药请神</t>
+  </si>
+  <si>
     <t>傩戏开场</t>
   </si>
   <si>
@@ -224,132 +272,90 @@
     <t>直到你的回合结束时，随机佩戴一个面具（从十殿阎罗、孟婆、二郎真君中随机选择）。</t>
   </si>
   <si>
-    <t>阎王震慑</t>
+    <t>面具傩戏</t>
+  </si>
+  <si>
+    <t>阎罗傩戏</t>
+  </si>
+  <si>
+    <t>二郎神请神</t>
   </si>
   <si>
     <t>2;20;10</t>
   </si>
   <si>
-    <t>阎王万我</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
   </si>
   <si>
     <t>1;0;1;100;5;1</t>
   </si>
   <si>
-    <t>阎王吸魂</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，获得{1}点护甲。</t>
   </si>
   <si>
     <t>1;2</t>
   </si>
   <si>
-    <t>阎王炼魂</t>
-  </si>
-  <si>
-    <t>阎王慷慨</t>
-  </si>
-  <si>
     <t>获得{0}点护甲，然后摸{1}张牌。</t>
   </si>
   <si>
     <t>1;1</t>
   </si>
   <si>
-    <t>阎王静心</t>
-  </si>
-  <si>
-    <t>阎王碎魂</t>
-  </si>
-  <si>
     <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。敌人的死期减少{3}。</t>
   </si>
   <si>
     <t>2;0;100;1</t>
   </si>
   <si>
-    <t>面具傩戏</t>
-  </si>
-  <si>
     <t>此牌无效。</t>
   </si>
   <si>
-    <t>无常震慑</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。有{3}%的概率额外打出一次此牌。</t>
   </si>
   <si>
     <t>2;10;10;50</t>
   </si>
   <si>
-    <t>无常万我</t>
-  </si>
-  <si>
     <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
   </si>
   <si>
     <t>1;0;50;3;1;100</t>
   </si>
   <si>
-    <t>无常吸魂</t>
-  </si>
-  <si>
     <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。有{2}%的概率额外打出一次此牌。</t>
   </si>
   <si>
     <t>1;5;50</t>
   </si>
   <si>
-    <t>无常自力</t>
-  </si>
-  <si>
-    <t>阎罗震慑</t>
-  </si>
-  <si>
     <t>2;30;30</t>
   </si>
   <si>
-    <t>阎罗吸魂</t>
-  </si>
-  <si>
     <t>3;3</t>
   </si>
   <si>
-    <t>阎罗傩戏</t>
-  </si>
-  <si>
     <t>随机切换一个律令（可能重复）。</t>
   </si>
   <si>
     <t>孟婆汤中的攻击牌+1。</t>
   </si>
   <si>
-    <t>孟婆熬药功能</t>
-  </si>
-  <si>
     <t>孟婆汤中的功能牌+1。</t>
   </si>
   <si>
-    <t>孟婆熬药请神</t>
-  </si>
-  <si>
     <t>孟婆汤中的请神牌+1。</t>
   </si>
   <si>
-    <t>二郎神请神</t>
-  </si>
-  <si>
     <t>拔舌鬼攻击</t>
   </si>
   <si>
     <t>造成{0}点伤害，重复{1}次。打出后有{2}%几率结束回合。</t>
   </si>
   <si>
+    <t>1;1;100</t>
+  </si>
+  <si>
     <t>穷鬼吸血</t>
   </si>
   <si>
@@ -365,28 +371,40 @@
     <t>防御</t>
   </si>
   <si>
+    <t>5;100</t>
+  </si>
+  <si>
     <t>铜柱鬼攻击</t>
   </si>
   <si>
     <t>造成{0}点伤害。打出后有{1}%几率结束回合。</t>
   </si>
   <si>
+    <t>10;100</t>
+  </si>
+  <si>
     <t>肉山鬼攻击</t>
   </si>
   <si>
     <t>水鬼攻击</t>
   </si>
   <si>
+    <t>1;100</t>
+  </si>
+  <si>
     <t>阎王攻击</t>
   </si>
   <si>
+    <t>2;100</t>
+  </si>
+  <si>
     <t>阎王空过</t>
   </si>
   <si>
     <t>喝咖啡</t>
   </si>
   <si>
-    <t>无事发生。打出后有{1}%几率结束回合。</t>
+    <t>无事发生。打出后有{0}%几率结束回合。</t>
   </si>
   <si>
     <t>阎王叠甲</t>
@@ -1079,7 +1097,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1090,33 +1108,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1438,16 +1459,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q54"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:R53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="5" width="32.8928571428571" customWidth="1"/>
-    <col min="6" max="6" width="64.3303571428571" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1696428571429" customWidth="1"/>
-    <col min="9" max="9" width="12.0446428571429" customWidth="1"/>
+    <col min="2" max="5" width="32.8916666666667" customWidth="1"/>
+    <col min="6" max="6" width="64.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="15.1666666666667" customWidth="1"/>
+    <col min="9" max="9" width="12.0416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:17">
+    <row r="1" s="1" customFormat="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1472,19 +1493,19 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="10"/>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:17">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="5"/>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:18">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1509,33 +1530,33 @@
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="11"/>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:17">
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="7"/>
+    </row>
+    <row r="3" s="3" customFormat="1" spans="1:18">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="12"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="9"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:18">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1546,942 +1567,1245 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:16">
-      <c r="B5" s="4" t="s">
+    <row r="5" customFormat="1" spans="1:18">
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="10">
         <v>2</v>
       </c>
-      <c r="H5" s="5" t="b">
+      <c r="H5" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" s="12"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="2:10">
-      <c r="B6" s="4" t="s">
+    <row r="6" customFormat="1" spans="1:18">
+      <c r="B6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" customFormat="1" spans="2:10">
-      <c r="B7" s="4" t="s">
+      <c r="H6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="K6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:18">
+      <c r="B7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="13"/>
+      <c r="O7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:18">
+      <c r="B8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R8" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:18">
+      <c r="B9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R9" s="13"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:18">
+      <c r="B10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R10" s="13"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:18">
+      <c r="B11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R11" s="13"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:18">
+      <c r="B12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R12" s="13"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:18">
+      <c r="B13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="10">
+        <v>100</v>
+      </c>
+      <c r="H13" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="13"/>
+      <c r="K13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13" s="13"/>
+      <c r="O13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R13" s="13"/>
+    </row>
+    <row r="14" customFormat="1" spans="1:18">
+      <c r="B14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="R14" s="13"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:18">
+      <c r="B15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="10">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="R15" s="13"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:18">
+      <c r="B16" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="2:14">
+      <c r="B17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1</v>
+      </c>
+      <c r="H17" s="11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="11"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+    </row>
+    <row r="18" customFormat="1" spans="2:14">
+      <c r="B18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" customFormat="1" spans="2:10">
-      <c r="B8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="C18" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="5" t="b">
+      <c r="D18" s="11"/>
+      <c r="E18" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+    </row>
+    <row r="19" customFormat="1" spans="2:14">
+      <c r="B19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="11"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" customFormat="1" spans="2:14">
+      <c r="B20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" customFormat="1" spans="2:10">
-      <c r="B9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="b">
+      <c r="J20" s="11"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+    </row>
+    <row r="21" customFormat="1" spans="2:14">
+      <c r="B21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="10">
+        <v>2</v>
+      </c>
+      <c r="H21" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" customFormat="1" spans="2:10">
-      <c r="B10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="5" t="b">
+      <c r="J21" s="11"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="13"/>
+    </row>
+    <row r="22" customFormat="1" spans="2:14">
+      <c r="B22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H22" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" customFormat="1" spans="2:10">
-      <c r="B11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12" customFormat="1" spans="2:8">
-      <c r="B12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="J22" s="11"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="13"/>
+    </row>
+    <row r="23" customFormat="1" spans="2:14">
+      <c r="B23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="2:8">
-      <c r="B13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="4">
-        <v>100</v>
-      </c>
-      <c r="H13" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="2:8">
-      <c r="B14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="H14" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="1" spans="2:8">
-      <c r="B15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="D23" s="11"/>
+      <c r="E23" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="4">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="b">
+      <c r="G23" s="10"/>
+      <c r="H23" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="11"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="13"/>
+    </row>
+    <row r="24" customFormat="1" spans="2:14">
+      <c r="B24" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" customFormat="1" spans="2:14">
+      <c r="B25" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25" s="11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" customFormat="1" spans="2:8">
-      <c r="B16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="1" spans="2:8">
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="J25" s="13"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="13"/>
+    </row>
+    <row r="26" customFormat="1" spans="2:14">
+      <c r="B26" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G17" s="4">
-        <v>1</v>
-      </c>
-      <c r="H17" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customFormat="1" spans="2:8">
-      <c r="B18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" customFormat="1" spans="2:8">
-      <c r="B19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" customFormat="1" spans="2:8">
-      <c r="B20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="2:8">
-      <c r="B21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G21" s="4">
-        <v>2</v>
-      </c>
-      <c r="H21" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="2:8">
-      <c r="B22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customFormat="1" spans="2:8">
-      <c r="B23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="2:8">
-      <c r="B24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="1" spans="2:8">
-      <c r="B25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="H25" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="1" spans="2:8">
-      <c r="B26" s="6" t="s">
+      <c r="D26" s="12"/>
+      <c r="E26" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="12" t="s">
         <v>23</v>
       </c>
       <c r="G26">
         <v>3</v>
       </c>
-      <c r="H26" s="5" t="b">
+      <c r="H26" s="11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" customFormat="1" spans="2:8">
-      <c r="B27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C27" s="4" t="s">
+      <c r="J26" s="12"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="13"/>
+    </row>
+    <row r="27" customFormat="1" spans="2:14">
+      <c r="B27" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="2:8">
-      <c r="B28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="4" t="s">
+      <c r="D27" s="12"/>
+      <c r="E27" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="13"/>
+    </row>
+    <row r="28" customFormat="1" spans="2:14">
+      <c r="B28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>86</v>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
-      </c>
-      <c r="H28" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="1" spans="2:8">
-      <c r="B29" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+    </row>
+    <row r="29" customFormat="1" spans="2:14">
+      <c r="B29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="5" t="b">
+      <c r="D29" s="12"/>
+      <c r="E29" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H29" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="2:8">
-      <c r="B30" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>54</v>
+    <row r="30" customFormat="1" spans="2:14">
+      <c r="B30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="G30">
         <v>50</v>
       </c>
-      <c r="H30" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="2:8">
-      <c r="B31" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="4" t="s">
+      <c r="H30" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="2:14">
+      <c r="B31" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="D31" s="12"/>
+      <c r="E31" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="2:8">
-      <c r="B32" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="G31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H31" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" spans="2:14">
+      <c r="B32" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H32" s="5" t="b">
+      <c r="D32" s="12"/>
+      <c r="E32" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H32" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:8">
-      <c r="B33" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="H33" s="5" t="b">
+      <c r="B33" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H33" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="2:8">
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="12"/>
+      <c r="E34" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H34" s="5" t="b">
+      <c r="F34" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H34" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="2:8">
-      <c r="B35" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H35" s="5" t="b">
+      <c r="B35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="2:8">
-      <c r="B36" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H36" s="5" t="b">
+      <c r="B36" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="H36" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="2:8">
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6" t="s">
+      <c r="D37" s="12"/>
+      <c r="E37" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>43</v>
+      <c r="F37" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="G37">
         <v>2</v>
       </c>
-      <c r="H37" s="5" t="b">
+      <c r="H37" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="2:8">
-      <c r="B38" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>43</v>
+      <c r="B38" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
-      <c r="H38" s="5" t="b">
+      <c r="H38" s="11" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="B39" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="5" t="b">
+      <c r="F39" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39" t="s">
+        <v>107</v>
+      </c>
+      <c r="H39" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="6" t="s">
+      <c r="B40" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G40" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="H40" s="5" t="b">
+      <c r="H40" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H41" s="5" t="b">
+      <c r="B41" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" s="6" t="s">
+      <c r="B42" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G42" t="s">
+        <v>116</v>
+      </c>
+      <c r="H42" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G43" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G44" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G45" t="s">
+        <v>121</v>
+      </c>
+      <c r="H45" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G46">
+        <v>100</v>
+      </c>
+      <c r="H46" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="B47" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H42" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8">
-      <c r="B43" s="6" t="s">
+      <c r="F47" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G47" t="s">
         <v>113</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="H47" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="B48" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="G48" t="s">
+        <v>119</v>
+      </c>
+      <c r="H48" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
+      <c r="B49" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G49" t="s">
+        <v>113</v>
+      </c>
+      <c r="H49" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
+      <c r="B50" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F50" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
+      <c r="B51" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G51" t="s">
+        <v>121</v>
+      </c>
+      <c r="H51" s="11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
+      <c r="B52" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="H43" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8">
-      <c r="B44" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H44" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8">
-      <c r="B45" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H45" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8">
-      <c r="B46" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="H46" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8">
-      <c r="B47" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H47" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8">
-      <c r="B48" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H48" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8">
-      <c r="B49" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="H49" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8">
-      <c r="B50" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8">
-      <c r="B51" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="H51" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8">
-      <c r="B52" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="H52" s="5" t="b">
+      <c r="F52" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G52" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="8:8">
-      <c r="H54" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:B53">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B53" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="3">

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -353,16 +353,19 @@
     <t>造成{0}点伤害，重复{1}次。打出后有{2}%几率结束回合。</t>
   </si>
   <si>
+    <t>1;2;100</t>
+  </si>
+  <si>
+    <t>穷鬼吸血</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>对本我造成{0}点伤害，自己恢复{1}点生命。打出后有{2}%几率结束回合。</t>
+  </si>
+  <si>
     <t>1;1;100</t>
-  </si>
-  <si>
-    <t>穷鬼吸血</t>
-  </si>
-  <si>
-    <t>吸血</t>
-  </si>
-  <si>
-    <t>对本我造成{0}点伤害，自己恢复{1}点生命。打出后有{2}%几率结束回合。</t>
   </si>
   <si>
     <t>铜柱鬼叠甲</t>
@@ -1097,7 +1100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1132,9 +1135,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1600,7 +1600,7 @@
         <v>27</v>
       </c>
       <c r="M5" s="12"/>
-      <c r="N5" s="13"/>
+      <c r="N5" s="12"/>
       <c r="O5" s="12" t="s">
         <v>28</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="L7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="13"/>
+      <c r="N7" s="12"/>
       <c r="O7" s="12" t="s">
         <v>28</v>
       </c>
@@ -1788,15 +1788,15 @@
       <c r="J9" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="13"/>
-      <c r="N9" s="13"/>
+      <c r="L9" s="12"/>
+      <c r="N9" s="12"/>
       <c r="O9" s="12" t="s">
         <v>28</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="R9" s="13"/>
+      <c r="R9" s="12"/>
     </row>
     <row r="10" customFormat="1" spans="1:18">
       <c r="B10" s="10" t="s">
@@ -1824,15 +1824,15 @@
       <c r="J10" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="L10" s="12"/>
+      <c r="N10" s="12"/>
       <c r="O10" s="12" t="s">
         <v>28</v>
       </c>
       <c r="P10" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="R10" s="13"/>
+      <c r="R10" s="12"/>
     </row>
     <row r="11" customFormat="1" spans="1:18">
       <c r="B11" s="10" t="s">
@@ -1860,15 +1860,15 @@
       <c r="J11" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="13"/>
-      <c r="N11" s="13"/>
+      <c r="L11" s="12"/>
+      <c r="N11" s="12"/>
       <c r="O11" s="12" t="s">
         <v>28</v>
       </c>
       <c r="P11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="R11" s="13"/>
+      <c r="R11" s="12"/>
     </row>
     <row r="12" customFormat="1" spans="1:18">
       <c r="B12" s="10" t="s">
@@ -1890,16 +1890,16 @@
       <c r="H12" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="J12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="N12" s="12"/>
       <c r="O12" s="12" t="s">
         <v>28</v>
       </c>
       <c r="P12" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="R12" s="13"/>
+      <c r="R12" s="12"/>
     </row>
     <row r="13" customFormat="1" spans="1:18">
       <c r="B13" s="10" t="s">
@@ -1921,21 +1921,21 @@
       <c r="H13" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="13"/>
+      <c r="J13" s="12"/>
       <c r="K13" s="12" t="s">
         <v>26</v>
       </c>
       <c r="L13" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="N13" s="13"/>
+      <c r="N13" s="12"/>
       <c r="O13" s="12" t="s">
         <v>28</v>
       </c>
       <c r="P13" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="R13" s="13"/>
+      <c r="R13" s="12"/>
     </row>
     <row r="14" customFormat="1" spans="1:18">
       <c r="B14" s="10" t="s">
@@ -1963,15 +1963,15 @@
       <c r="J14" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="L14" s="12"/>
+      <c r="N14" s="12"/>
       <c r="O14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="P14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="R14" s="13"/>
+      <c r="R14" s="12"/>
     </row>
     <row r="15" customFormat="1" spans="1:18">
       <c r="B15" s="10" t="s">
@@ -1993,16 +1993,16 @@
       <c r="H15" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="N15" s="13"/>
+      <c r="J15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="N15" s="12"/>
       <c r="O15" s="12" t="s">
         <v>28</v>
       </c>
       <c r="P15" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="R15" s="13"/>
+      <c r="R15" s="12"/>
     </row>
     <row r="16" customFormat="1" spans="1:18">
       <c r="B16" s="10" t="s">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="J17" s="11"/>
       <c r="K17" s="12"/>
-      <c r="L17" s="13"/>
+      <c r="L17" s="12"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="12"/>
-      <c r="L19" s="13"/>
+      <c r="L19" s="12"/>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
     </row>
@@ -2178,10 +2178,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="11"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
       <c r="M21" s="12"/>
-      <c r="N21" s="13"/>
+      <c r="N21" s="12"/>
     </row>
     <row r="22" customFormat="1" spans="2:14">
       <c r="B22" s="11" t="s">
@@ -2204,10 +2204,10 @@
         <v>0</v>
       </c>
       <c r="J22" s="11"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
       <c r="M22" s="12"/>
-      <c r="N22" s="13"/>
+      <c r="N22" s="12"/>
     </row>
     <row r="23" customFormat="1" spans="2:14">
       <c r="B23" s="11" t="s">
@@ -2228,10 +2228,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="11"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
       <c r="M23" s="12"/>
-      <c r="N23" s="13"/>
+      <c r="N23" s="12"/>
     </row>
     <row r="24" customFormat="1" spans="2:14">
       <c r="B24" s="12" t="s">
@@ -2253,11 +2253,11 @@
       <c r="H24" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
       <c r="M24" s="12"/>
-      <c r="N24" s="13"/>
+      <c r="N24" s="12"/>
     </row>
     <row r="25" customFormat="1" spans="2:14">
       <c r="B25" s="12" t="s">
@@ -2276,11 +2276,11 @@
       <c r="H25" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="J25" s="13"/>
+      <c r="J25" s="12"/>
       <c r="K25" s="12"/>
-      <c r="L25" s="13"/>
+      <c r="L25" s="12"/>
       <c r="M25" s="12"/>
-      <c r="N25" s="13"/>
+      <c r="N25" s="12"/>
     </row>
     <row r="26" customFormat="1" spans="2:14">
       <c r="B26" s="12" t="s">
@@ -2303,10 +2303,10 @@
         <v>0</v>
       </c>
       <c r="J26" s="12"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
       <c r="M26" s="12"/>
-      <c r="N26" s="13"/>
+      <c r="N26" s="12"/>
     </row>
     <row r="27" customFormat="1" spans="2:14">
       <c r="B27" s="12" t="s">
@@ -2328,11 +2328,11 @@
       <c r="H27" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
       <c r="M27" s="12"/>
-      <c r="N27" s="13"/>
+      <c r="N27" s="12"/>
     </row>
     <row r="28" customFormat="1" spans="2:14">
       <c r="B28" s="12" t="s">
@@ -2586,7 +2586,7 @@
         <v>110</v>
       </c>
       <c r="G40" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H40" s="11" t="b">
         <v>1</v>
@@ -2594,16 +2594,16 @@
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H41" s="11" t="b">
         <v>1</v>
@@ -2611,16 +2611,16 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D42" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H42" s="11" t="b">
         <v>1</v>
@@ -2628,13 +2628,13 @@
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G43" t="s">
         <v>61</v>
@@ -2645,16 +2645,16 @@
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G44" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H44" s="11" t="b">
         <v>1</v>
@@ -2662,16 +2662,16 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H45" s="11" t="b">
         <v>1</v>
@@ -2679,13 +2679,13 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -2696,16 +2696,16 @@
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H47" s="11" t="b">
         <v>1</v>
@@ -2713,16 +2713,16 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H48" s="11" t="b">
         <v>1</v>
@@ -2730,16 +2730,16 @@
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G49" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H49" s="11" t="b">
         <v>1</v>
@@ -2747,13 +2747,13 @@
     </row>
     <row r="50" spans="2:8">
       <c r="B50" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G50" t="s">
         <v>61</v>
@@ -2764,16 +2764,16 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G51" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H51" s="11" t="b">
         <v>1</v>
@@ -2781,10 +2781,10 @@
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>60</v>
@@ -2798,7 +2798,7 @@
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="167">
   <si>
     <t>##var</t>
   </si>
@@ -438,6 +438,99 @@
   </si>
   <si>
     <t>结束回合</t>
+  </si>
+  <si>
+    <t>孟婆汤_攻击一</t>
+  </si>
+  <si>
+    <t>孟婆汤_攻击二</t>
+  </si>
+  <si>
+    <t>孟婆汤_攻击三</t>
+  </si>
+  <si>
+    <t>孟婆汤_功能一</t>
+  </si>
+  <si>
+    <t>孟婆汤_功能二</t>
+  </si>
+  <si>
+    <t>孟婆汤_功能三</t>
+  </si>
+  <si>
+    <t>孟婆汤_请神</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF功能药水_12</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF功能药水_13</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混功能药水_121</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混功能药水_131</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF攻击药水_21</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF平衡药水_2</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF功能药水_23</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_211</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混平衡药水_2</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_231</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF攻击药水_31</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF攻击药水_32</t>
+  </si>
+  <si>
+    <t>孟婆汤_AF平衡药水_3</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_311</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混攻击药水_321</t>
+  </si>
+  <si>
+    <t>孟婆汤_三混平衡药水_3</t>
+  </si>
+  <si>
+    <t>孟婆汤_AI平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_AI攻击药水_21</t>
+  </si>
+  <si>
+    <t>孟婆汤_AI攻击药水_31</t>
+  </si>
+  <si>
+    <t>孟婆汤_FI平衡药水_1</t>
+  </si>
+  <si>
+    <t>孟婆汤_FI功能药水_21</t>
+  </si>
+  <si>
+    <t>孟婆汤_FI功能药水_31</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1116,20 +1209,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1138,6 +1225,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1459,7 +1549,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="5" width="32.8916666666667" customWidth="1"/>
@@ -1503,7 +1593,8 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
-      <c r="Q1" s="5"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
     </row>
     <row r="2" s="2" customFormat="1" spans="1:18">
       <c r="A2" s="2" t="s">
@@ -1530,31 +1621,33 @@
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="7"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:18">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="9"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:18">
       <c r="A4" s="1" t="s">
@@ -1566,1233 +1659,1243 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
     </row>
     <row r="5" customFormat="1" spans="1:18">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>2</v>
       </c>
-      <c r="H5" s="11" t="b">
+      <c r="H5" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12" t="s">
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="12" t="s">
+      <c r="P5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="R5" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:18">
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="12" t="s">
+      <c r="H6" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="12" t="s">
+      <c r="P6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="12" t="s">
+      <c r="R6" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:18">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="12" t="s">
+      <c r="H7" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12" t="s">
+      <c r="N7" s="10"/>
+      <c r="O7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="P7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="Q7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="R7" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:18">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="11" t="b">
+      <c r="H8" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="12" t="s">
+      <c r="N8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P8" s="12" t="s">
+      <c r="P8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="Q8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R8" s="12" t="s">
+      <c r="R8" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:18">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="10">
-        <v>1</v>
-      </c>
-      <c r="H9" s="11" t="b">
+      <c r="G9" s="8">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12" t="s">
+      <c r="L9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P9" s="12" t="s">
+      <c r="P9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R9" s="12"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="1" spans="1:18">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="11" t="b">
+      <c r="H10" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12" t="s">
+      <c r="L10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P10" s="12" t="s">
+      <c r="P10" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R10" s="12"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="1" spans="1:18">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="12" t="s">
+      <c r="H11" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12" t="s">
+      <c r="L11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P11" s="12" t="s">
+      <c r="P11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R11" s="12"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="1" spans="1:18">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10" t="s">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12" t="s">
+      <c r="H12" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P12" s="12" t="s">
+      <c r="P12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R12" s="12"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="1" spans="1:18">
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10" t="s">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>100</v>
       </c>
-      <c r="H13" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12" t="s">
+      <c r="H13" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12" t="s">
+      <c r="N13" s="10"/>
+      <c r="O13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P13" s="12" t="s">
+      <c r="P13" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R13" s="12"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="1" spans="1:18">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="12" t="s">
+      <c r="H14" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12" t="s">
+      <c r="L14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P14" s="12" t="s">
+      <c r="P14" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="R14" s="12"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="1" spans="1:18">
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="10">
-        <v>1</v>
-      </c>
-      <c r="H15" s="11" t="b">
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12" t="s">
+      <c r="J15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P15" s="12" t="s">
+      <c r="P15" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="R15" s="12"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" customFormat="1" spans="1:18">
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="11" t="b">
+      <c r="G16" s="8"/>
+      <c r="H16" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="I16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="K16" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="12" t="s">
+      <c r="L16" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N16" s="12" t="s">
+      <c r="N16" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="O16" s="12" t="s">
+      <c r="O16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="P16" s="12" t="s">
+      <c r="P16" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="Q16" s="12" t="s">
+      <c r="Q16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="R16" s="12" t="s">
+      <c r="R16" s="10" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="2:14">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11" t="s">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="10">
-        <v>1</v>
-      </c>
-      <c r="H17" s="11" t="b">
+      <c r="G17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
     </row>
     <row r="18" customFormat="1" spans="2:14">
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11" t="s">
+      <c r="D18" s="9"/>
+      <c r="E18" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
+      <c r="H18" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
     </row>
     <row r="19" customFormat="1" spans="2:14">
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11" t="s">
+      <c r="D19" s="9"/>
+      <c r="E19" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="11"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
+      <c r="H19" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
     </row>
     <row r="20" customFormat="1" spans="2:14">
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11" t="s">
+      <c r="D20" s="9"/>
+      <c r="E20" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="H20" s="11" t="b">
+      <c r="H20" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="J20" s="11"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
     </row>
     <row r="21" customFormat="1" spans="2:14">
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11" t="s">
+      <c r="D21" s="9"/>
+      <c r="E21" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="8">
         <v>2</v>
       </c>
-      <c r="H21" s="11" t="b">
+      <c r="H21" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="11"/>
-      <c r="K21" s="12"/>
-      <c r="L21" s="12"/>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
     </row>
     <row r="22" customFormat="1" spans="2:14">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11" t="s">
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="11" t="b">
+      <c r="H22" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="J22" s="11"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
     </row>
     <row r="23" customFormat="1" spans="2:14">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11" t="s">
+      <c r="D23" s="9"/>
+      <c r="E23" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" s="11"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="12"/>
-      <c r="M23" s="12"/>
-      <c r="N23" s="12"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="9"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
     </row>
     <row r="24" customFormat="1" spans="2:14">
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12" t="s">
+      <c r="D24" s="10"/>
+      <c r="E24" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" s="12"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="12"/>
-      <c r="N24" s="12"/>
+      <c r="H24" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
     </row>
     <row r="25" customFormat="1" spans="2:14">
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12" t="s">
+      <c r="D25" s="10"/>
+      <c r="E25" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="11" t="b">
+      <c r="H25" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
     </row>
     <row r="26" customFormat="1" spans="2:14">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12" t="s">
+      <c r="D26" s="10"/>
+      <c r="E26" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="10" t="s">
         <v>23</v>
       </c>
       <c r="G26">
         <v>3</v>
       </c>
-      <c r="H26" s="11" t="b">
+      <c r="H26" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
     </row>
     <row r="27" customFormat="1" spans="2:14">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12" t="s">
+      <c r="D27" s="10"/>
+      <c r="E27" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
+      <c r="H27" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
     </row>
     <row r="28" customFormat="1" spans="2:14">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12" t="s">
+      <c r="D28" s="10"/>
+      <c r="E28" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="8" t="s">
         <v>95</v>
       </c>
       <c r="G28" t="s">
         <v>96</v>
       </c>
-      <c r="H28" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
+      <c r="H28" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
     </row>
     <row r="29" customFormat="1" spans="2:14">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12" t="s">
+      <c r="D29" s="10"/>
+      <c r="E29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H29" s="11" t="b">
+      <c r="H29" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="2:14">
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12" t="s">
+      <c r="D30" s="10"/>
+      <c r="E30" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="8" t="s">
         <v>67</v>
       </c>
       <c r="G30">
         <v>50</v>
       </c>
-      <c r="H30" s="11" t="b">
+      <c r="H30" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="2:14">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12" t="s">
+      <c r="D31" s="10"/>
+      <c r="E31" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="11" t="b">
+      <c r="H31" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="2:14">
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12" t="s">
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H32" s="11" t="b">
+      <c r="H32" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:8">
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12" t="s">
+      <c r="D33" s="10"/>
+      <c r="E33" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H33" s="11" t="b">
+      <c r="H33" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="2:8">
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12" t="s">
+      <c r="D34" s="10"/>
+      <c r="E34" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="H34" s="11" t="b">
+      <c r="H34" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="2:8">
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12" t="s">
+      <c r="D35" s="10"/>
+      <c r="E35" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H35" s="11" t="b">
+      <c r="H35" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="2:8">
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12" t="s">
+      <c r="D36" s="10"/>
+      <c r="E36" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="11" t="b">
+      <c r="H36" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="2:8">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12" t="s">
+      <c r="D37" s="10"/>
+      <c r="E37" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="10" t="s">
         <v>52</v>
       </c>
       <c r="G37">
         <v>2</v>
       </c>
-      <c r="H37" s="11" t="b">
+      <c r="H37" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="2:8">
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12" t="s">
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="10" t="s">
         <v>52</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
-      <c r="H38" s="11" t="b">
+      <c r="H38" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="10" t="s">
         <v>106</v>
       </c>
       <c r="G39" t="s">
         <v>107</v>
       </c>
-      <c r="H39" s="11" t="b">
+      <c r="H39" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="10" t="s">
         <v>110</v>
       </c>
       <c r="G40" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="11" t="b">
+      <c r="H40" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="10" t="s">
         <v>60</v>
       </c>
       <c r="G41" t="s">
         <v>114</v>
       </c>
-      <c r="H41" s="11" t="b">
+      <c r="H41" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="10" t="s">
         <v>116</v>
       </c>
       <c r="G42" t="s">
         <v>117</v>
       </c>
-      <c r="H42" s="11" t="b">
+      <c r="H42" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="2:8">
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="10" t="s">
         <v>116</v>
       </c>
       <c r="G43" t="s">
         <v>61</v>
       </c>
-      <c r="H43" s="11" t="b">
+      <c r="H43" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="10" t="s">
         <v>116</v>
       </c>
       <c r="G44" t="s">
         <v>120</v>
       </c>
-      <c r="H44" s="11" t="b">
+      <c r="H44" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8">
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="10" t="s">
         <v>116</v>
       </c>
       <c r="G45" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="11" t="b">
+      <c r="H45" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="10" t="s">
         <v>125</v>
       </c>
       <c r="G46">
         <v>100</v>
       </c>
-      <c r="H46" s="11" t="b">
+      <c r="H46" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="10" t="s">
         <v>60</v>
       </c>
       <c r="G47" t="s">
         <v>114</v>
       </c>
-      <c r="H47" s="11" t="b">
+      <c r="H47" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="10" t="s">
         <v>128</v>
       </c>
       <c r="G48" t="s">
         <v>120</v>
       </c>
-      <c r="H48" s="11" t="b">
+      <c r="H48" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8">
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="10" t="s">
         <v>130</v>
       </c>
       <c r="G49" t="s">
         <v>114</v>
       </c>
-      <c r="H49" s="11" t="b">
+      <c r="H49" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="2:8">
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="10" t="s">
         <v>116</v>
       </c>
       <c r="G50" t="s">
         <v>61</v>
       </c>
-      <c r="H50" s="11" t="b">
+      <c r="H50" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:8">
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="10" t="s">
         <v>133</v>
       </c>
       <c r="G51" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="11" t="b">
+      <c r="H51" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:8">
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="10" t="s">
         <v>60</v>
       </c>
       <c r="G52" t="s">
         <v>61</v>
       </c>
-      <c r="H52" s="11" t="b">
+      <c r="H52" s="9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2802,16 +2905,172 @@
       </c>
       <c r="H53" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
+      <c r="B54" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
+      <c r="B55" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8">
+      <c r="B56" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8">
+      <c r="B57" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8">
+      <c r="B58" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
+      <c r="B59" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
+      <c r="B60" s="11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8">
+      <c r="B61" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8">
+      <c r="B62" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
+      <c r="B63" s="11" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
+      <c r="B64" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="11" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="11" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="11" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="11" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B53" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <mergeCells count="3">
-    <mergeCell ref="I1:P1"/>
-    <mergeCell ref="I2:P2"/>
-    <mergeCell ref="I3:P3"/>
+  <mergeCells count="4">
+    <mergeCell ref="I1:R1"/>
+    <mergeCell ref="I2:R2"/>
+    <mergeCell ref="I3:R3"/>
+    <mergeCell ref="I4:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -10,7 +10,7 @@
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardTable!$B$1:$B$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CardTable!$B$1:$B$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1193,7 +1193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1213,9 +1213,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1659,1243 +1656,1243 @@
       <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
     </row>
     <row r="5" customFormat="1" spans="1:18">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>2</v>
       </c>
-      <c r="H5" s="9" t="b">
+      <c r="H5" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="10" t="s">
+      <c r="L5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10" t="s">
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="R5" s="10" t="s">
+      <c r="R5" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:18">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="10" t="s">
+      <c r="H6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="M6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Q6" s="10" t="s">
+      <c r="Q6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="10" t="s">
+      <c r="R6" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:18">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="H7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10" t="s">
+      <c r="N7" s="9"/>
+      <c r="O7" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="10" t="s">
+      <c r="Q7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="R7" s="10" t="s">
+      <c r="R7" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:18">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="9" t="b">
+      <c r="H8" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="Q8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="R8" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:18">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="9" t="b">
+      <c r="G9" s="7">
+        <v>1</v>
+      </c>
+      <c r="H9" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10" t="s">
+      <c r="L9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P9" s="10" t="s">
+      <c r="P9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="R9" s="9"/>
     </row>
     <row r="10" customFormat="1" spans="1:18">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="9" t="b">
+      <c r="H10" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10" t="s">
+      <c r="L10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P10" s="10" t="s">
+      <c r="P10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R10" s="10"/>
+      <c r="R10" s="9"/>
     </row>
     <row r="11" customFormat="1" spans="1:18">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="H11" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="L11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10" t="s">
+      <c r="L11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R11" s="10"/>
+      <c r="R11" s="9"/>
     </row>
     <row r="12" customFormat="1" spans="1:18">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10" t="s">
+      <c r="H12" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P12" s="10" t="s">
+      <c r="P12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R12" s="10"/>
+      <c r="R12" s="9"/>
     </row>
     <row r="13" customFormat="1" spans="1:18">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="7">
         <v>100</v>
       </c>
-      <c r="H13" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10" t="s">
+      <c r="H13" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10" t="s">
+      <c r="N13" s="9"/>
+      <c r="O13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="P13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R13" s="10"/>
+      <c r="R13" s="9"/>
     </row>
     <row r="14" customFormat="1" spans="1:18">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="H14" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="10" t="s">
+      <c r="H14" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="L14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10" t="s">
+      <c r="L14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P14" s="10" t="s">
+      <c r="P14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R14" s="10"/>
+      <c r="R14" s="9"/>
     </row>
     <row r="15" customFormat="1" spans="1:18">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="8">
-        <v>1</v>
-      </c>
-      <c r="H15" s="9" t="b">
+      <c r="G15" s="7">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10" t="s">
+      <c r="J15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P15" s="10" t="s">
+      <c r="P15" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="R15" s="10"/>
+      <c r="R15" s="9"/>
     </row>
     <row r="16" customFormat="1" spans="1:18">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="9" t="b">
+      <c r="G16" s="7"/>
+      <c r="H16" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="10" t="s">
+      <c r="J16" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="K16" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="10" t="s">
+      <c r="L16" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="M16" s="10" t="s">
+      <c r="M16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="N16" s="10" t="s">
+      <c r="N16" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="O16" s="10" t="s">
+      <c r="O16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="P16" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="Q16" s="10" t="s">
+      <c r="Q16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="R16" s="10" t="s">
+      <c r="R16" s="9" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="2:14">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="8">
-        <v>1</v>
-      </c>
-      <c r="H17" s="9" t="b">
+      <c r="G17" s="7">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
     </row>
     <row r="18" customFormat="1" spans="2:14">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
+      <c r="H18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
     </row>
     <row r="19" customFormat="1" spans="2:14">
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="H19" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
+      <c r="H19" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
     </row>
     <row r="20" customFormat="1" spans="2:14">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9" t="s">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="H20" s="9" t="b">
+      <c r="H20" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
     </row>
     <row r="21" customFormat="1" spans="2:14">
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9" t="s">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="7">
         <v>2</v>
       </c>
-      <c r="H21" s="9" t="b">
+      <c r="H21" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
     </row>
     <row r="22" customFormat="1" spans="2:14">
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="9" t="b">
+      <c r="H22" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J22" s="9"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
     </row>
     <row r="23" customFormat="1" spans="2:14">
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
     </row>
     <row r="24" customFormat="1" spans="2:14">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="9"/>
+      <c r="E24" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
+      <c r="H24" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
     </row>
     <row r="25" customFormat="1" spans="2:14">
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10" t="s">
+      <c r="D25" s="9"/>
+      <c r="E25" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="9" t="b">
+      <c r="H25" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
     </row>
     <row r="26" customFormat="1" spans="2:14">
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10" t="s">
+      <c r="D26" s="9"/>
+      <c r="E26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="9" t="s">
         <v>23</v>
       </c>
       <c r="G26">
         <v>3</v>
       </c>
-      <c r="H26" s="9" t="b">
+      <c r="H26" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
     </row>
     <row r="27" customFormat="1" spans="2:14">
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10" t="s">
+      <c r="D27" s="9"/>
+      <c r="E27" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
+      <c r="H27" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
     </row>
     <row r="28" customFormat="1" spans="2:14">
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10" t="s">
+      <c r="D28" s="9"/>
+      <c r="E28" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="7" t="s">
         <v>95</v>
       </c>
       <c r="G28" t="s">
         <v>96</v>
       </c>
-      <c r="H28" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
+      <c r="H28" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
     </row>
     <row r="29" customFormat="1" spans="2:14">
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10" t="s">
+      <c r="D29" s="9"/>
+      <c r="E29" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H29" s="9" t="b">
+      <c r="H29" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="2:14">
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10" t="s">
+      <c r="D30" s="9"/>
+      <c r="E30" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="7" t="s">
         <v>67</v>
       </c>
       <c r="G30">
         <v>50</v>
       </c>
-      <c r="H30" s="9" t="b">
+      <c r="H30" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="2:14">
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10" t="s">
+      <c r="D31" s="9"/>
+      <c r="E31" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="H31" s="9" t="b">
+      <c r="H31" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="2:14">
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10" t="s">
+      <c r="D32" s="9"/>
+      <c r="E32" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H32" s="9" t="b">
+      <c r="H32" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:8">
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10" t="s">
+      <c r="D33" s="9"/>
+      <c r="E33" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H33" s="9" t="b">
+      <c r="H33" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="2:8">
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10" t="s">
+      <c r="D34" s="9"/>
+      <c r="E34" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="H34" s="9" t="b">
+      <c r="H34" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="2:8">
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10" t="s">
+      <c r="D35" s="9"/>
+      <c r="E35" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H35" s="9" t="b">
+      <c r="H35" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="2:8">
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10" t="s">
+      <c r="D36" s="9"/>
+      <c r="E36" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="H36" s="9" t="b">
+      <c r="H36" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="2:8">
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10" t="s">
+      <c r="D37" s="9"/>
+      <c r="E37" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="9" t="s">
         <v>52</v>
       </c>
       <c r="G37">
         <v>2</v>
       </c>
-      <c r="H37" s="9" t="b">
+      <c r="H37" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="2:8">
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10" t="s">
+      <c r="D38" s="9"/>
+      <c r="E38" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="9" t="s">
         <v>52</v>
       </c>
       <c r="G38">
         <v>2</v>
       </c>
-      <c r="H38" s="9" t="b">
+      <c r="H38" s="8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:8">
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="9" t="s">
         <v>106</v>
       </c>
       <c r="G39" t="s">
         <v>107</v>
       </c>
-      <c r="H39" s="9" t="b">
+      <c r="H39" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="2:8">
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G40" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="9" t="b">
+      <c r="H40" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="2:8">
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="9" t="s">
         <v>60</v>
       </c>
       <c r="G41" t="s">
         <v>114</v>
       </c>
-      <c r="H41" s="9" t="b">
+      <c r="H41" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="2:8">
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="9" t="s">
         <v>116</v>
       </c>
       <c r="G42" t="s">
         <v>117</v>
       </c>
-      <c r="H42" s="9" t="b">
+      <c r="H42" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="2:8">
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="9" t="s">
         <v>116</v>
       </c>
       <c r="G43" t="s">
         <v>61</v>
       </c>
-      <c r="H43" s="9" t="b">
+      <c r="H43" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="2:8">
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="9" t="s">
         <v>116</v>
       </c>
       <c r="G44" t="s">
         <v>120</v>
       </c>
-      <c r="H44" s="9" t="b">
+      <c r="H44" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:8">
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="9" t="s">
         <v>116</v>
       </c>
       <c r="G45" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="9" t="b">
+      <c r="H45" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="9" t="s">
         <v>125</v>
       </c>
       <c r="G46">
         <v>100</v>
       </c>
-      <c r="H46" s="9" t="b">
+      <c r="H46" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F47" s="10" t="s">
+      <c r="F47" s="9" t="s">
         <v>60</v>
       </c>
       <c r="G47" t="s">
         <v>114</v>
       </c>
-      <c r="H47" s="9" t="b">
+      <c r="H47" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="9" t="s">
         <v>128</v>
       </c>
       <c r="G48" t="s">
         <v>120</v>
       </c>
-      <c r="H48" s="9" t="b">
+      <c r="H48" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:8">
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F49" s="10" t="s">
+      <c r="F49" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G49" t="s">
-        <v>114</v>
-      </c>
-      <c r="H49" s="9" t="b">
+        <v>117</v>
+      </c>
+      <c r="H49" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="2:8">
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="9" t="s">
         <v>116</v>
       </c>
       <c r="G50" t="s">
         <v>61</v>
       </c>
-      <c r="H50" s="9" t="b">
+      <c r="H50" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="2:8">
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="9" t="s">
         <v>133</v>
       </c>
       <c r="G51" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="9" t="b">
+      <c r="H51" s="8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="2:8">
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="9" t="s">
         <v>60</v>
       </c>
       <c r="G52" t="s">
         <v>61</v>
       </c>
-      <c r="H52" s="9" t="b">
+      <c r="H52" s="8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2908,162 +2905,162 @@
       </c>
     </row>
     <row r="54" spans="2:8">
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="10" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="55" spans="2:8">
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="56" spans="2:8">
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="57" spans="2:8">
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="58" spans="2:8">
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="10" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="59" spans="2:8">
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="10" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="60" spans="2:8">
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="10" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="61" spans="2:8">
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="10" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="62" spans="2:8">
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="10" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="63" spans="2:8">
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="10" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="64" spans="2:8">
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="10" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="65" spans="2:2">
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="10" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="66" spans="2:2">
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="67" spans="2:2">
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="10" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="10" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="70" spans="2:2">
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="10" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="71" spans="2:2">
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="10" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="73" spans="2:2">
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="10" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="74" spans="2:2">
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="10" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="10" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="10" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="77" spans="2:2">
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="10" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="10" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="79" spans="2:2">
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="10" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="10" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="10" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="10" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="10" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="84" spans="2:2">
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="10" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B53" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B84" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="4">

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="168">
   <si>
     <t>##var</t>
   </si>
@@ -302,6 +302,9 @@
     <t>1;1</t>
   </si>
   <si>
+    <t>3;70</t>
+  </si>
+  <si>
     <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。敌人的死期减少{3}。</t>
   </si>
   <si>
@@ -314,7 +317,7 @@
     <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。有{3}%的概率额外打出一次此牌。</t>
   </si>
   <si>
-    <t>2;10;10;50</t>
+    <t>2;10;10;30</t>
   </si>
   <si>
     <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
@@ -326,7 +329,7 @@
     <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。有{2}%的概率额外打出一次此牌。</t>
   </si>
   <si>
-    <t>1;5;50</t>
+    <t>1;5;30</t>
   </si>
   <si>
     <t>2;30;30</t>
@@ -2323,7 +2326,9 @@
       <c r="F23" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G23" s="7"/>
+      <c r="G23" s="7" t="s">
+        <v>90</v>
+      </c>
       <c r="H23" s="8" t="b">
         <v>1</v>
       </c>
@@ -2345,10 +2350,10 @@
         <v>72</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" s="8" t="b">
         <v>1</v>
@@ -2371,7 +2376,7 @@
         <v>80</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" s="8" t="b">
         <v>0</v>
@@ -2420,10 +2425,10 @@
         <v>36</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H27" s="8" t="b">
         <v>1</v>
@@ -2446,10 +2451,10 @@
         <v>43</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H28" s="8" t="b">
         <v>1</v>
@@ -2472,10 +2477,10 @@
         <v>48</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H29" s="8" t="b">
         <v>0</v>
@@ -2517,7 +2522,7 @@
         <v>33</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H31" s="8" t="b">
         <v>1</v>
@@ -2538,7 +2543,7 @@
         <v>45</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H32" s="8" t="b">
         <v>0</v>
@@ -2556,7 +2561,7 @@
         <v>81</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H33" s="8" t="b">
         <v>0</v>
@@ -2574,7 +2579,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" s="8" t="b">
         <v>0</v>
@@ -2592,7 +2597,7 @@
         <v>54</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H35" s="8" t="b">
         <v>0</v>
@@ -2610,7 +2615,7 @@
         <v>76</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H36" s="8" t="b">
         <v>0</v>
@@ -2660,16 +2665,16 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G39" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H39" s="8" t="b">
         <v>1</v>
@@ -2677,16 +2682,16 @@
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H40" s="8" t="b">
         <v>1</v>
@@ -2694,16 +2699,16 @@
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H41" s="8" t="b">
         <v>1</v>
@@ -2711,16 +2716,16 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G42" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H42" s="8" t="b">
         <v>1</v>
@@ -2728,13 +2733,13 @@
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G43" t="s">
         <v>61</v>
@@ -2745,16 +2750,16 @@
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G44" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H44" s="8" t="b">
         <v>1</v>
@@ -2762,16 +2767,16 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G45" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H45" s="8" t="b">
         <v>1</v>
@@ -2779,13 +2784,13 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -2796,16 +2801,16 @@
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H47" s="8" t="b">
         <v>1</v>
@@ -2813,16 +2818,16 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H48" s="8" t="b">
         <v>1</v>
@@ -2830,16 +2835,16 @@
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G49" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H49" s="8" t="b">
         <v>1</v>
@@ -2847,13 +2852,13 @@
     </row>
     <row r="50" spans="2:8">
       <c r="B50" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G50" t="s">
         <v>61</v>
@@ -2864,16 +2869,16 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H51" s="8" t="b">
         <v>1</v>
@@ -2881,10 +2886,10 @@
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>60</v>
@@ -2898,7 +2903,7 @@
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2906,157 +2911,157 @@
     </row>
     <row r="54" spans="2:8">
       <c r="B54" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="2:8">
       <c r="B59" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="B62" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78" spans="2:2">
       <c r="B78" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="2:2">
       <c r="B79" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="80" spans="2:2">
       <c r="B80" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="209">
   <si>
     <t>##var</t>
   </si>
@@ -281,75 +281,138 @@
     <t>二郎神请神</t>
   </si>
   <si>
+    <t>暂作抵抗</t>
+  </si>
+  <si>
+    <t>阎王压迫</t>
+  </si>
+  <si>
     <t>2;20;10</t>
   </si>
   <si>
+    <t>强魂万我</t>
+  </si>
+  <si>
     <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
   </si>
   <si>
     <t>1;0;1;100;5;1</t>
   </si>
   <si>
+    <t>聚魂</t>
+  </si>
+  <si>
     <t>造成{0}点伤害，获得{1}点护甲。</t>
   </si>
   <si>
     <t>1;2</t>
   </si>
   <si>
+    <t>强炼魂</t>
+  </si>
+  <si>
+    <t>凝魂</t>
+  </si>
+  <si>
     <t>获得{0}点护甲，然后摸{1}张牌。</t>
   </si>
   <si>
     <t>1;1</t>
   </si>
   <si>
+    <t>强心</t>
+  </si>
+  <si>
     <t>3;70</t>
   </si>
   <si>
+    <t>漫天冥气</t>
+  </si>
+  <si>
     <t>受到{0}点伤害，然后使你下一次受到的伤害改为{1}。打出后有{2}%几率结束回合。敌人的死期减少{3}。</t>
   </si>
   <si>
     <t>2;0;100;1</t>
   </si>
   <si>
+    <t>已有神助</t>
+  </si>
+  <si>
     <t>此牌无效。</t>
   </si>
   <si>
+    <t>强击</t>
+  </si>
+  <si>
+    <t>拘魂</t>
+  </si>
+  <si>
     <t>造成{0}点伤害，有{1}%几率斩杀对手。打出后有{2}%几率结束回合。有{3}%的概率额外打出一次此牌。</t>
   </si>
   <si>
     <t>2;10;10;30</t>
   </si>
   <si>
+    <t>驱罪为己</t>
+  </si>
+  <si>
     <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
   </si>
   <si>
     <t>1;0;50;3;1;100</t>
   </si>
   <si>
+    <t>勾魂</t>
+  </si>
+  <si>
     <t>造成{0}点伤害。若有敌人因此牌的伤害死亡，你恢复{1}点生命。有{2}%的概率额外打出一次此牌。</t>
   </si>
   <si>
     <t>1;5;30</t>
   </si>
   <si>
+    <t>黑白相连</t>
+  </si>
+  <si>
+    <t>十殿齐发</t>
+  </si>
+  <si>
     <t>2;30;30</t>
   </si>
   <si>
+    <t>魂归我用</t>
+  </si>
+  <si>
     <t>3;3</t>
   </si>
   <si>
+    <t>判官笔</t>
+  </si>
+  <si>
     <t>随机切换一个律令（可能重复）。</t>
   </si>
   <si>
+    <t>材料：红</t>
+  </si>
+  <si>
     <t>孟婆汤中的攻击牌+1。</t>
   </si>
   <si>
+    <t>材料：蓝</t>
+  </si>
+  <si>
     <t>孟婆汤中的功能牌+1。</t>
   </si>
   <si>
+    <t>材料：黄</t>
+  </si>
+  <si>
     <t>孟婆汤中的请神牌+1。</t>
   </si>
   <si>
+    <t>看破</t>
+  </si>
+  <si>
     <t>拔舌鬼攻击</t>
   </si>
   <si>
@@ -464,63 +527,120 @@
     <t>孟婆汤_请神</t>
   </si>
   <si>
+    <t>摸{0}张牌。</t>
+  </si>
+  <si>
     <t>孟婆汤_AF平衡药水_1</t>
   </si>
   <si>
     <t>孟婆汤_AF功能药水_12</t>
   </si>
   <si>
+    <t>1;3</t>
+  </si>
+  <si>
     <t>孟婆汤_AF功能药水_13</t>
   </si>
   <si>
+    <t>1;4</t>
+  </si>
+  <si>
     <t>孟婆汤_三混平衡药水_1</t>
   </si>
   <si>
+    <t>造成{0}点伤害，获得{1}点护甲，摸{2}张牌。</t>
+  </si>
+  <si>
+    <t>2;2;2</t>
+  </si>
+  <si>
     <t>孟婆汤_三混功能药水_121</t>
   </si>
   <si>
+    <t>1;4;1</t>
+  </si>
+  <si>
     <t>孟婆汤_三混功能药水_131</t>
   </si>
   <si>
+    <t>1;5;1</t>
+  </si>
+  <si>
     <t>孟婆汤_AF攻击药水_21</t>
   </si>
   <si>
+    <t>3;1</t>
+  </si>
+  <si>
     <t>孟婆汤_AF平衡药水_2</t>
   </si>
   <si>
     <t>孟婆汤_AF功能药水_23</t>
   </si>
   <si>
+    <t>2;4</t>
+  </si>
+  <si>
     <t>孟婆汤_三混攻击药水_211</t>
   </si>
   <si>
+    <t>4;1;1</t>
+  </si>
+  <si>
     <t>孟婆汤_三混平衡药水_2</t>
   </si>
   <si>
+    <t>3;3;3</t>
+  </si>
+  <si>
     <t>孟婆汤_三混攻击药水_231</t>
   </si>
   <si>
+    <t>2;5;1</t>
+  </si>
+  <si>
     <t>孟婆汤_AF攻击药水_31</t>
   </si>
   <si>
+    <t>4;1</t>
+  </si>
+  <si>
     <t>孟婆汤_AF攻击药水_32</t>
   </si>
   <si>
+    <t>4;2</t>
+  </si>
+  <si>
     <t>孟婆汤_AF平衡药水_3</t>
   </si>
   <si>
+    <t>4;4</t>
+  </si>
+  <si>
     <t>孟婆汤_三混攻击药水_311</t>
   </si>
   <si>
+    <t>5;1;1</t>
+  </si>
+  <si>
     <t>孟婆汤_三混攻击药水_321</t>
   </si>
   <si>
+    <t>5;2;1</t>
+  </si>
+  <si>
     <t>孟婆汤_三混平衡药水_3</t>
   </si>
   <si>
+    <t>4;4;4</t>
+  </si>
+  <si>
     <t>孟婆汤_AI平衡药水_1</t>
   </si>
   <si>
+    <t>造成{0}点伤害，摸{1}张牌。</t>
+  </si>
+  <si>
     <t>孟婆汤_AI攻击药水_21</t>
   </si>
   <si>
@@ -528,6 +648,9 @@
   </si>
   <si>
     <t>孟婆汤_FI平衡药水_1</t>
+  </si>
+  <si>
+    <t>获得{0}点护甲，摸{1}张牌。</t>
   </si>
   <si>
     <t>孟婆汤_FI功能药水_21</t>
@@ -2165,7 +2288,7 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>52</v>
@@ -2191,13 +2314,13 @@
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H18" s="8" t="b">
         <v>1</v>
@@ -2217,13 +2340,13 @@
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H19" s="8" t="b">
         <v>1</v>
@@ -2243,13 +2366,13 @@
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H20" s="8" t="b">
         <v>0</v>
@@ -2269,7 +2392,7 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>52</v>
@@ -2295,13 +2418,13 @@
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H22" s="8" t="b">
         <v>0</v>
@@ -2321,13 +2444,13 @@
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>60</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="H23" s="8" t="b">
         <v>1</v>
@@ -2347,13 +2470,13 @@
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="9" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H24" s="8" t="b">
         <v>1</v>
@@ -2373,10 +2496,10 @@
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="9" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="H25" s="8" t="b">
         <v>0</v>
@@ -2396,7 +2519,7 @@
       </c>
       <c r="D26" s="9"/>
       <c r="E26" s="9" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>23</v>
@@ -2422,13 +2545,13 @@
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H27" s="8" t="b">
         <v>1</v>
@@ -2448,13 +2571,13 @@
       </c>
       <c r="D28" s="9"/>
       <c r="E28" s="9" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G28" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="H28" s="8" t="b">
         <v>1</v>
@@ -2474,13 +2597,13 @@
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H29" s="8" t="b">
         <v>0</v>
@@ -2495,7 +2618,7 @@
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="9" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>67</v>
@@ -2516,13 +2639,13 @@
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="9" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="H31" s="8" t="b">
         <v>1</v>
@@ -2537,13 +2660,13 @@
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="9" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>45</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H32" s="8" t="b">
         <v>0</v>
@@ -2558,10 +2681,10 @@
       </c>
       <c r="D33" s="9"/>
       <c r="E33" s="9" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="H33" s="8" t="b">
         <v>0</v>
@@ -2576,10 +2699,10 @@
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="9" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="H34" s="8" t="b">
         <v>0</v>
@@ -2594,10 +2717,10 @@
       </c>
       <c r="D35" s="9"/>
       <c r="E35" s="9" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="H35" s="8" t="b">
         <v>0</v>
@@ -2612,10 +2735,10 @@
       </c>
       <c r="D36" s="9"/>
       <c r="E36" s="9" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="H36" s="8" t="b">
         <v>0</v>
@@ -2630,7 +2753,7 @@
       </c>
       <c r="D37" s="9"/>
       <c r="E37" s="9" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>52</v>
@@ -2651,7 +2774,7 @@
       </c>
       <c r="D38" s="9"/>
       <c r="E38" s="9" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>52</v>
@@ -2665,16 +2788,16 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="9" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="G39" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="H39" s="8" t="b">
         <v>1</v>
@@ -2682,16 +2805,16 @@
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="9" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="G40" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="H40" s="8" t="b">
         <v>1</v>
@@ -2699,16 +2822,16 @@
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="9" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H41" s="8" t="b">
         <v>1</v>
@@ -2716,16 +2839,16 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="9" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="H42" s="8" t="b">
         <v>1</v>
@@ -2733,13 +2856,13 @@
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="9" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="G43" t="s">
         <v>61</v>
@@ -2750,16 +2873,16 @@
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="9" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H44" s="8" t="b">
         <v>1</v>
@@ -2767,16 +2890,16 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="9" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="G45" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="H45" s="8" t="b">
         <v>1</v>
@@ -2784,13 +2907,13 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="9" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G46">
         <v>100</v>
@@ -2801,16 +2924,16 @@
     </row>
     <row r="47" spans="2:8">
       <c r="B47" s="9" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="H47" s="8" t="b">
         <v>1</v>
@@ -2818,16 +2941,16 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" s="9" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="G48" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H48" s="8" t="b">
         <v>1</v>
@@ -2835,16 +2958,16 @@
     </row>
     <row r="49" spans="2:8">
       <c r="B49" s="9" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="G49" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="H49" s="8" t="b">
         <v>1</v>
@@ -2852,13 +2975,13 @@
     </row>
     <row r="50" spans="2:8">
       <c r="B50" s="9" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="G50" t="s">
         <v>61</v>
@@ -2869,16 +2992,16 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" s="9" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>22</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="G51" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="H51" s="8" t="b">
         <v>1</v>
@@ -2886,10 +3009,10 @@
     </row>
     <row r="52" spans="2:8">
       <c r="B52" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" s="9" t="s">
         <v>135</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>114</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>60</v>
@@ -2903,7 +3026,7 @@
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2911,157 +3034,343 @@
     </row>
     <row r="54" spans="2:8">
       <c r="B54" s="10" t="s">
-        <v>137</v>
+        <v>158</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" s="10" t="s">
-        <v>138</v>
+        <v>159</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55">
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="2:8">
       <c r="B56" s="10" t="s">
-        <v>139</v>
+        <v>160</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56">
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" s="10" t="s">
-        <v>140</v>
+        <v>161</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" s="10" t="s">
-        <v>141</v>
+        <v>162</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G58">
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="2:8">
       <c r="B59" s="10" t="s">
-        <v>142</v>
+        <v>163</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59">
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" s="10" t="s">
-        <v>143</v>
+        <v>164</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" s="10" t="s">
-        <v>144</v>
+        <v>166</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="2:8">
       <c r="B62" s="10" t="s">
-        <v>145</v>
+        <v>167</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G62" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" s="10" t="s">
-        <v>146</v>
+        <v>169</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G63" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" s="10" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2">
+        <v>171</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G64" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7">
       <c r="B65" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2">
+        <v>174</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G65" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7">
       <c r="B66" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2">
+        <v>176</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G66" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7">
       <c r="B67" s="10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2">
+        <v>178</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G67" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7">
       <c r="B68" s="10" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2">
+        <v>180</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G68" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7">
       <c r="B69" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2">
+        <v>181</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G69" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7">
       <c r="B70" s="10" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2">
+        <v>183</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G70" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7">
       <c r="B71" s="10" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2">
+        <v>185</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G71" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7">
       <c r="B72" s="10" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2">
+        <v>187</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G72" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7">
       <c r="B73" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2">
+        <v>189</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G73" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7">
       <c r="B74" s="10" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2">
+        <v>191</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G74" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7">
       <c r="B75" s="10" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2">
+        <v>193</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G75" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
       <c r="B76" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2">
+        <v>195</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G76" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7">
       <c r="B77" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2">
+        <v>197</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G77" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7">
       <c r="B78" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2">
+        <v>199</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G78" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7">
       <c r="B79" s="10" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2">
+        <v>201</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G79" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
       <c r="B80" s="10" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2">
+        <v>203</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G80" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7">
       <c r="B81" s="10" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2">
+        <v>204</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G81" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7">
       <c r="B82" s="10" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2">
+        <v>205</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G82" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7">
       <c r="B83" s="10" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2">
+        <v>207</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G83" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7">
       <c r="B84" s="10" t="s">
-        <v>167</v>
+        <v>208</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G84" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -296,7 +296,7 @@
     <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
   </si>
   <si>
-    <t>1;0;1;100;5;1</t>
+    <t>1;0;1;100;3;1</t>
   </si>
   <si>
     <t>聚魂</t>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -155,7 +155,7 @@
     <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。</t>
   </si>
   <si>
-    <t>1;0;1;100</t>
+    <t>1;1;1;100</t>
   </si>
   <si>
     <t>阎王万我</t>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -323,7 +323,7 @@
     <t>强心</t>
   </si>
   <si>
-    <t>3;70</t>
+    <t>3;60</t>
   </si>
   <si>
     <t>漫天冥气</t>

--- a/Configs/source/Datas/card.xlsx
+++ b/Configs/source/Datas/card.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="21000" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="CardTable" sheetId="1" r:id="rId1"/>
@@ -296,7 +296,7 @@
     <t>造成{0}点伤害，重复{1}次。打出后伤害次数永久增加{2}，并且有{3}%几率结束回合。若你造成的伤害次数不小于{4}，受到伤害的敌人死期减少{5}。</t>
   </si>
   <si>
-    <t>1;0;1;100;3;1</t>
+    <t>1;1;1;100;3;1</t>
   </si>
   <si>
     <t>聚魂</t>
@@ -359,7 +359,7 @@
     <t>造成{0}点伤害，重复{1}次，有{2}%的概率使伤害次数增加{3}。打出后伤害次数永久增加{4}，并且有{5}%几率结束回合。</t>
   </si>
   <si>
-    <t>1;0;50;3;1;100</t>
+    <t>2;1;50;1;1;100</t>
   </si>
   <si>
     <t>勾魂</t>
